--- a/docs/data/jp/xlsx/6737.xlsx
+++ b/docs/data/jp/xlsx/6737.xlsx
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -323,6 +323,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -717,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC178"/>
+  <dimension ref="A1:AC185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4305,10 +4308,12 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 ()</t>
-        </is>
-      </c>
-      <c r="B47" s="29" t="n"/>
+          <t>현재 주가 (2026.10.26)</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="n">
+        <v>3105</v>
+      </c>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="31" t="n"/>
       <c r="E47" s="31" t="n"/>
@@ -4343,7 +4348,9 @@
           <t>발행주식수 (보통주)</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n"/>
+      <c r="B48" s="29" t="n">
+        <v>42330820</v>
+      </c>
       <c r="C48" s="30" t="n"/>
       <c r="D48" s="31" t="n"/>
       <c r="E48" s="31" t="n"/>
@@ -5542,7 +5549,7 @@
     <row r="74">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C74" s="41" t="n"/>
@@ -5794,1550 +5801,1584 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G79" s="17">
+        <f>IF(OR(G78="",C78=""),"",IF(C78&lt;=0,"",IFERROR(G78/C78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H79" s="17">
+        <f>IF(OR(H78="",D78=""),"",IF(D78&lt;=0,"",IFERROR(H78/D78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I79" s="17">
+        <f>IF(OR(I78="",E78=""),"",IF(E78&lt;=0,"",IFERROR(I78/E78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J79" s="17">
+        <f>IF(OR(J78="",F78=""),"",IF(F78&lt;=0,"",IFERROR(J78/F78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K79" s="17">
+        <f>IF(OR(K78="",G78=""),"",IF(G78&lt;=0,"",IFERROR(K78/G78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L79" s="17">
+        <f>IF(OR(L78="",H78=""),"",IF(H78&lt;=0,"",IFERROR(L78/H78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M79" s="17">
+        <f>IF(OR(M78="",I78=""),"",IF(I78&lt;=0,"",IFERROR(M78/I78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N79" s="17">
+        <f>IF(OR(N78="",J78=""),"",IF(J78&lt;=0,"",IFERROR(N78/J78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T79" s="17">
+        <f>IF(OR(T78="",S78=""),"",IF(S78&lt;=0,"",IFERROR(T78/S78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U79" s="17">
+        <f>IF(OR(U78="",T78=""),"",IF(T78&lt;=0,"",IFERROR(U78/T78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V79" s="17">
+        <f>IF(OR(V78="",U78=""),"",IF(U78&lt;=0,"",IFERROR(V78/U78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W79" s="17">
+        <f>IF(OR(W78="",V78=""),"",IF(V78&lt;=0,"",IFERROR(W78/V78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X79" s="17">
+        <f>IF(OR(X78="",W78=""),"",IF(W78&lt;=0,"",IFERROR(X78/W78-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="C79" s="22" t="n">
+      <c r="C80" s="22" t="n">
         <v>12684</v>
       </c>
-      <c r="D79" s="22" t="n">
+      <c r="D80" s="22" t="n">
         <v>14549</v>
       </c>
-      <c r="E79" s="22" t="n">
+      <c r="E80" s="22" t="n">
         <v>15607</v>
       </c>
-      <c r="F79" s="22" t="n">
+      <c r="F80" s="22" t="n">
         <v>12347</v>
       </c>
-      <c r="G79" s="22" t="n">
+      <c r="G80" s="22" t="n">
         <v>12500</v>
       </c>
-      <c r="H79" s="22" t="n">
+      <c r="H80" s="22" t="n">
         <v>14087</v>
       </c>
-      <c r="I79" s="22" t="n">
+      <c r="I80" s="22" t="n">
         <v>15359</v>
       </c>
-      <c r="J79" s="22" t="n">
+      <c r="J80" s="22" t="n">
         <v>11498</v>
       </c>
-      <c r="K79" s="22" t="n">
+      <c r="K80" s="22" t="n">
         <v>14029</v>
       </c>
-      <c r="L79" s="22" t="n">
+      <c r="L80" s="22" t="n">
         <v>14185</v>
       </c>
-      <c r="M79" s="22" t="n">
+      <c r="M80" s="22" t="n">
         <v>15695</v>
       </c>
-      <c r="N79" s="22" t="n">
+      <c r="N80" s="22" t="n">
         <v>13094</v>
       </c>
-      <c r="T79" s="22" t="n">
+      <c r="T80" s="22" t="n">
         <v>15129</v>
       </c>
-      <c r="U79" s="22" t="n">
+      <c r="U80" s="22" t="n">
         <v>16205</v>
       </c>
-      <c r="V79" s="22" t="n">
+      <c r="V80" s="22" t="n">
         <v>15607</v>
       </c>
-      <c r="W79" s="22" t="n">
+      <c r="W80" s="22" t="n">
         <v>15359</v>
       </c>
-      <c r="X79" s="22" t="n">
+      <c r="X80" s="22" t="n">
         <v>15695</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C80" s="12" t="n">
+      <c r="C81" s="12" t="n">
         <v>5953</v>
       </c>
-      <c r="D80" s="12" t="n">
+      <c r="D81" s="12" t="n">
         <v>6426</v>
       </c>
-      <c r="E80" s="12" t="n">
+      <c r="E81" s="12" t="n">
         <v>6704</v>
       </c>
-      <c r="F80" s="12" t="n">
+      <c r="F81" s="12" t="n">
         <v>5849</v>
       </c>
-      <c r="G80" s="12" t="n">
+      <c r="G81" s="12" t="n">
         <v>6120</v>
       </c>
-      <c r="H80" s="12" t="n">
+      <c r="H81" s="12" t="n">
         <v>7224</v>
       </c>
-      <c r="I80" s="12" t="n">
+      <c r="I81" s="12" t="n">
         <v>7006</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="J81" s="12" t="n">
         <v>5839</v>
       </c>
-      <c r="K80" s="12" t="n">
+      <c r="K81" s="12" t="n">
         <v>6507</v>
       </c>
-      <c r="L80" s="12" t="n">
+      <c r="L81" s="12" t="n">
         <v>6751</v>
       </c>
-      <c r="M80" s="12" t="n">
+      <c r="M81" s="12" t="n">
         <v>6804</v>
       </c>
-      <c r="N80" s="12" t="n">
+      <c r="N81" s="12" t="n">
         <v>6937</v>
       </c>
-      <c r="T80" s="12" t="n">
+      <c r="T81" s="12" t="n">
         <v>7943</v>
       </c>
-      <c r="U80" s="12" t="n">
+      <c r="U81" s="12" t="n">
         <v>7507</v>
       </c>
-      <c r="V80" s="12" t="n">
+      <c r="V81" s="12" t="n">
         <v>6704</v>
       </c>
-      <c r="W80" s="12" t="n">
+      <c r="W81" s="12" t="n">
         <v>7006</v>
       </c>
-      <c r="X80" s="12" t="n">
+      <c r="X81" s="12" t="n">
         <v>6804</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>판매비와 관리비</t>
-        </is>
-      </c>
-      <c r="C81" s="22" t="n">
-        <v>5375</v>
-      </c>
-      <c r="D81" s="22" t="n">
-        <v>5504</v>
-      </c>
-      <c r="E81" s="22" t="n">
-        <v>5354</v>
-      </c>
-      <c r="F81" s="22" t="n">
-        <v>5792</v>
-      </c>
-      <c r="G81" s="22" t="n">
-        <v>5347</v>
-      </c>
-      <c r="H81" s="22" t="n">
-        <v>5885</v>
-      </c>
-      <c r="I81" s="22" t="n">
-        <v>5469</v>
-      </c>
-      <c r="J81" s="22" t="n">
-        <v>5937</v>
-      </c>
-      <c r="K81" s="22" t="n">
-        <v>5749</v>
-      </c>
-      <c r="L81" s="22" t="n">
-        <v>6091</v>
-      </c>
-      <c r="M81" s="22" t="n">
-        <v>5758</v>
-      </c>
-      <c r="N81" s="22" t="n">
-        <v>6130</v>
-      </c>
-      <c r="T81" s="22" t="n">
-        <v>5054</v>
-      </c>
-      <c r="U81" s="22" t="n">
-        <v>5207</v>
-      </c>
-      <c r="V81" s="22" t="n">
-        <v>5354</v>
-      </c>
-      <c r="W81" s="22" t="n">
-        <v>5469</v>
-      </c>
-      <c r="X81" s="22" t="n">
-        <v>5758</v>
-      </c>
-    </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>영업이익(손실)</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="n">
-        <v>578</v>
-      </c>
-      <c r="D82" s="12" t="n">
-        <v>923</v>
-      </c>
-      <c r="E82" s="12" t="n">
-        <v>1349</v>
-      </c>
-      <c r="F82" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="G82" s="12" t="n">
-        <v>773</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>1338</v>
-      </c>
-      <c r="I82" s="12" t="n">
-        <v>1538</v>
-      </c>
-      <c r="J82" s="12" t="n">
-        <v>-97</v>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>756</v>
-      </c>
-      <c r="L82" s="12" t="n">
-        <v>660</v>
-      </c>
-      <c r="M82" s="12" t="n">
-        <v>1046</v>
-      </c>
-      <c r="N82" s="12" t="n">
-        <v>807</v>
-      </c>
-      <c r="T82" s="12" t="n">
-        <v>2890</v>
-      </c>
-      <c r="U82" s="12" t="n">
-        <v>2301</v>
-      </c>
-      <c r="V82" s="12" t="n">
-        <v>1349</v>
-      </c>
-      <c r="W82" s="12" t="n">
-        <v>1538</v>
-      </c>
-      <c r="X82" s="12" t="n">
-        <v>1046</v>
+      <c r="A82" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G82" s="17">
+        <f>IF(OR(G81="",C81=""),"",IF(C81&lt;=0,"",IFERROR(G81/C81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H82" s="17">
+        <f>IF(OR(H81="",D81=""),"",IF(D81&lt;=0,"",IFERROR(H81/D81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I82" s="17">
+        <f>IF(OR(I81="",E81=""),"",IF(E81&lt;=0,"",IFERROR(I81/E81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J82" s="17">
+        <f>IF(OR(J81="",F81=""),"",IF(F81&lt;=0,"",IFERROR(J81/F81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K82" s="17">
+        <f>IF(OR(K81="",G81=""),"",IF(G81&lt;=0,"",IFERROR(K81/G81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L82" s="17">
+        <f>IF(OR(L81="",H81=""),"",IF(H81&lt;=0,"",IFERROR(L81/H81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M82" s="17">
+        <f>IF(OR(M81="",I81=""),"",IF(I81&lt;=0,"",IFERROR(M81/I81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N82" s="17">
+        <f>IF(OR(N81="",J81=""),"",IF(J81&lt;=0,"",IFERROR(N81/J81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T82" s="17">
+        <f>IF(OR(T81="",S81=""),"",IF(S81&lt;=0,"",IFERROR(T81/S81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U82" s="17">
+        <f>IF(OR(U81="",T81=""),"",IF(T81&lt;=0,"",IFERROR(U81/T81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V82" s="17">
+        <f>IF(OR(V81="",U81=""),"",IF(U81&lt;=0,"",IFERROR(V81/U81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W82" s="17">
+        <f>IF(OR(W81="",V81=""),"",IF(V81&lt;=0,"",IFERROR(W81/V81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X82" s="17">
+        <f>IF(OR(X81="",W81=""),"",IF(W81&lt;=0,"",IFERROR(X81/W81-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>이자수익</t>
+          <t>판매비와 관리비</t>
         </is>
       </c>
       <c r="C83" s="22" t="n">
-        <v>4</v>
+        <v>5375</v>
       </c>
       <c r="D83" s="22" t="n">
-        <v>8</v>
+        <v>5504</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>13</v>
+        <v>5354</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>7</v>
+        <v>5792</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>1</v>
+        <v>5347</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>3</v>
+        <v>5885</v>
       </c>
       <c r="I83" s="22" t="n">
-        <v>7</v>
+        <v>5469</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>4</v>
+        <v>5937</v>
       </c>
       <c r="K83" s="22" t="n">
-        <v>20</v>
+        <v>5749</v>
       </c>
       <c r="L83" s="22" t="n">
-        <v>12</v>
+        <v>6091</v>
       </c>
       <c r="M83" s="22" t="n">
-        <v>20</v>
+        <v>5758</v>
       </c>
       <c r="N83" s="22" t="n">
-        <v>13</v>
+        <v>6130</v>
       </c>
       <c r="T83" s="22" t="n">
-        <v>7</v>
+        <v>5054</v>
       </c>
       <c r="U83" s="22" t="n">
-        <v>4</v>
+        <v>5207</v>
       </c>
       <c r="V83" s="22" t="n">
-        <v>13</v>
+        <v>5354</v>
       </c>
       <c r="W83" s="22" t="n">
-        <v>7</v>
+        <v>5469</v>
       </c>
       <c r="X83" s="22" t="n">
-        <v>20</v>
+        <v>5758</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>배당금수익</t>
-        </is>
-      </c>
-      <c r="C84" s="22" t="n">
-        <v>30</v>
-      </c>
-      <c r="D84" s="22" t="n">
-        <v>507</v>
-      </c>
-      <c r="E84" s="22" t="n">
-        <v>58</v>
-      </c>
-      <c r="F84" s="22" t="n">
-        <v>593</v>
-      </c>
-      <c r="G84" s="22" t="n">
-        <v>24</v>
-      </c>
-      <c r="H84" s="22" t="n">
-        <v>589</v>
-      </c>
-      <c r="I84" s="22" t="n">
-        <v>73</v>
-      </c>
-      <c r="J84" s="22" t="n">
-        <v>613</v>
-      </c>
-      <c r="K84" s="22" t="n">
-        <v>34</v>
-      </c>
-      <c r="L84" s="22" t="n">
-        <v>654</v>
-      </c>
-      <c r="M84" s="22" t="n">
-        <v>75</v>
-      </c>
-      <c r="N84" s="22" t="n">
-        <v>732</v>
-      </c>
-      <c r="T84" s="22" t="n">
-        <v>25</v>
-      </c>
-      <c r="U84" s="22" t="n">
-        <v>45</v>
-      </c>
-      <c r="V84" s="22" t="n">
-        <v>58</v>
-      </c>
-      <c r="W84" s="22" t="n">
-        <v>73</v>
-      </c>
-      <c r="X84" s="22" t="n">
-        <v>75</v>
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>영업이익(손실)</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="n">
+        <v>578</v>
+      </c>
+      <c r="D84" s="12" t="n">
+        <v>923</v>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>1349</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>773</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>1338</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>1538</v>
+      </c>
+      <c r="J84" s="12" t="n">
+        <v>-97</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>756</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>660</v>
+      </c>
+      <c r="M84" s="12" t="n">
+        <v>1046</v>
+      </c>
+      <c r="N84" s="12" t="n">
+        <v>807</v>
+      </c>
+      <c r="T84" s="12" t="n">
+        <v>2890</v>
+      </c>
+      <c r="U84" s="12" t="n">
+        <v>2301</v>
+      </c>
+      <c r="V84" s="12" t="n">
+        <v>1349</v>
+      </c>
+      <c r="W84" s="12" t="n">
+        <v>1538</v>
+      </c>
+      <c r="X84" s="12" t="n">
+        <v>1046</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="20" t="inlineStr">
-        <is>
-          <t>외환차익</t>
-        </is>
-      </c>
-      <c r="C85" s="22" t="n">
-        <v>-16</v>
-      </c>
-      <c r="D85" s="22" t="n">
-        <v>-183</v>
-      </c>
-      <c r="E85" s="22" t="n">
-        <v>306</v>
-      </c>
-      <c r="F85" s="22" t="n">
-        <v>365</v>
-      </c>
-      <c r="G85" s="22" t="n">
-        <v>-365</v>
-      </c>
-      <c r="H85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="22" t="n">
-        <v>159</v>
-      </c>
-      <c r="K85" s="22" t="n">
-        <v>-68</v>
-      </c>
-      <c r="L85" s="22" t="n">
-        <v>-8</v>
-      </c>
-      <c r="N85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V85" s="22" t="n">
-        <v>306</v>
-      </c>
-      <c r="W85" s="22" t="n">
-        <v>0</v>
+      <c r="A85" s="45" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C85" s="17">
+        <f>IF(OR(C84="",C78=""),"",IF(C78&lt;=0,"",IFERROR(C84/C78,"")))</f>
+        <v/>
+      </c>
+      <c r="D85" s="17">
+        <f>IF(OR(D84="",D78=""),"",IF(D78&lt;=0,"",IFERROR(D84/D78,"")))</f>
+        <v/>
+      </c>
+      <c r="E85" s="17">
+        <f>IF(OR(E84="",E78=""),"",IF(E78&lt;=0,"",IFERROR(E84/E78,"")))</f>
+        <v/>
+      </c>
+      <c r="F85" s="17">
+        <f>IF(OR(F84="",F78=""),"",IF(F78&lt;=0,"",IFERROR(F84/F78,"")))</f>
+        <v/>
+      </c>
+      <c r="G85" s="17">
+        <f>IF(OR(G84="",G78=""),"",IF(G78&lt;=0,"",IFERROR(G84/G78,"")))</f>
+        <v/>
+      </c>
+      <c r="H85" s="17">
+        <f>IF(OR(H84="",H78=""),"",IF(H78&lt;=0,"",IFERROR(H84/H78,"")))</f>
+        <v/>
+      </c>
+      <c r="I85" s="17">
+        <f>IF(OR(I84="",I78=""),"",IF(I78&lt;=0,"",IFERROR(I84/I78,"")))</f>
+        <v/>
+      </c>
+      <c r="J85" s="17">
+        <f>IF(OR(J84="",J78=""),"",IF(J78&lt;=0,"",IFERROR(J84/J78,"")))</f>
+        <v/>
+      </c>
+      <c r="K85" s="17">
+        <f>IF(OR(K84="",K78=""),"",IF(K78&lt;=0,"",IFERROR(K84/K78,"")))</f>
+        <v/>
+      </c>
+      <c r="L85" s="17">
+        <f>IF(OR(L84="",L78=""),"",IF(L78&lt;=0,"",IFERROR(L84/L78,"")))</f>
+        <v/>
+      </c>
+      <c r="M85" s="17">
+        <f>IF(OR(M84="",M78=""),"",IF(M78&lt;=0,"",IFERROR(M84/M78,"")))</f>
+        <v/>
+      </c>
+      <c r="N85" s="17">
+        <f>IF(OR(N84="",N78=""),"",IF(N78&lt;=0,"",IFERROR(N84/N78,"")))</f>
+        <v/>
+      </c>
+      <c r="T85" s="17">
+        <f>IF(OR(T84="",T78=""),"",IF(T78&lt;=0,"",IFERROR(T84/T78,"")))</f>
+        <v/>
+      </c>
+      <c r="U85" s="17">
+        <f>IF(OR(U84="",U78=""),"",IF(U78&lt;=0,"",IFERROR(U84/U78,"")))</f>
+        <v/>
+      </c>
+      <c r="V85" s="17">
+        <f>IF(OR(V84="",V78=""),"",IF(V78&lt;=0,"",IFERROR(V84/V78,"")))</f>
+        <v/>
+      </c>
+      <c r="W85" s="17">
+        <f>IF(OR(W84="",W78=""),"",IF(W78&lt;=0,"",IFERROR(W84/W78,"")))</f>
+        <v/>
+      </c>
+      <c r="X85" s="17">
+        <f>IF(OR(X84="",X78=""),"",IF(X78&lt;=0,"",IFERROR(X84/X78,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C86" s="22" t="n">
-        <v>151</v>
-      </c>
-      <c r="D86" s="22" t="n">
-        <v>126</v>
-      </c>
-      <c r="E86" s="22" t="n">
-        <v>105</v>
-      </c>
-      <c r="F86" s="22" t="n">
-        <v>79</v>
-      </c>
-      <c r="G86" s="22" t="n">
-        <v>122</v>
-      </c>
-      <c r="H86" s="22" t="n">
-        <v>77</v>
-      </c>
-      <c r="I86" s="22" t="n">
-        <v>76</v>
-      </c>
-      <c r="J86" s="22" t="n">
-        <v>75</v>
-      </c>
-      <c r="K86" s="22" t="n">
-        <v>123</v>
-      </c>
-      <c r="L86" s="22" t="n">
-        <v>81</v>
-      </c>
-      <c r="M86" s="22" t="n">
-        <v>89</v>
-      </c>
-      <c r="N86" s="22" t="n">
-        <v>97</v>
-      </c>
-      <c r="T86" s="22" t="n">
-        <v>30</v>
-      </c>
-      <c r="U86" s="22" t="n">
-        <v>60</v>
-      </c>
-      <c r="V86" s="22" t="n">
-        <v>105</v>
-      </c>
-      <c r="W86" s="22" t="n">
-        <v>76</v>
-      </c>
-      <c r="X86" s="22" t="n">
-        <v>89</v>
+      <c r="A86" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G86" s="17">
+        <f>IF(OR(G84="",C84=""),"",IF(C84&lt;=0,"",IFERROR(G84/C84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H86" s="17">
+        <f>IF(OR(H84="",D84=""),"",IF(D84&lt;=0,"",IFERROR(H84/D84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I86" s="17">
+        <f>IF(OR(I84="",E84=""),"",IF(E84&lt;=0,"",IFERROR(I84/E84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J86" s="17">
+        <f>IF(OR(J84="",F84=""),"",IF(F84&lt;=0,"",IFERROR(J84/F84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K86" s="17">
+        <f>IF(OR(K84="",G84=""),"",IF(G84&lt;=0,"",IFERROR(K84/G84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L86" s="17">
+        <f>IF(OR(L84="",H84=""),"",IF(H84&lt;=0,"",IFERROR(L84/H84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M86" s="17">
+        <f>IF(OR(M84="",I84=""),"",IF(I84&lt;=0,"",IFERROR(M84/I84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N86" s="17">
+        <f>IF(OR(N84="",J84=""),"",IF(J84&lt;=0,"",IFERROR(N84/J84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T86" s="17">
+        <f>IF(OR(T84="",S84=""),"",IF(S84&lt;=0,"",IFERROR(T84/S84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U86" s="17">
+        <f>IF(OR(U84="",T84=""),"",IF(T84&lt;=0,"",IFERROR(U84/T84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V86" s="17">
+        <f>IF(OR(V84="",U84=""),"",IF(U84&lt;=0,"",IFERROR(V84/U84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W86" s="17">
+        <f>IF(OR(W84="",V84=""),"",IF(V84&lt;=0,"",IFERROR(W84/V84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X86" s="17">
+        <f>IF(OR(X84="",W84=""),"",IF(W84&lt;=0,"",IFERROR(X84/W84-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>영업외수익 합계</t>
+          <t>이자수익</t>
         </is>
       </c>
       <c r="C87" s="22" t="n">
-        <v>167</v>
+        <v>4</v>
       </c>
       <c r="D87" s="22" t="n">
-        <v>460</v>
+        <v>8</v>
       </c>
       <c r="E87" s="22" t="n">
-        <v>482</v>
+        <v>13</v>
       </c>
       <c r="F87" s="22" t="n">
-        <v>1046</v>
+        <v>7</v>
       </c>
       <c r="G87" s="22" t="n">
-        <v>-219</v>
+        <v>1</v>
       </c>
       <c r="H87" s="22" t="n">
-        <v>669</v>
+        <v>3</v>
       </c>
       <c r="I87" s="22" t="n">
-        <v>156</v>
+        <v>7</v>
       </c>
       <c r="J87" s="22" t="n">
-        <v>853</v>
+        <v>4</v>
       </c>
       <c r="K87" s="22" t="n">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="L87" s="22" t="n">
-        <v>739</v>
+        <v>12</v>
       </c>
       <c r="M87" s="22" t="n">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="N87" s="22" t="n">
-        <v>844</v>
+        <v>13</v>
       </c>
       <c r="T87" s="22" t="n">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="U87" s="22" t="n">
-        <v>108</v>
+        <v>4</v>
       </c>
       <c r="V87" s="22" t="n">
-        <v>482</v>
+        <v>13</v>
       </c>
       <c r="W87" s="22" t="n">
-        <v>156</v>
+        <v>7</v>
       </c>
       <c r="X87" s="22" t="n">
-        <v>101</v>
+        <v>20</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
+          <t>배당금수익</t>
         </is>
       </c>
       <c r="C88" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="D88" s="22" t="n">
+        <v>507</v>
+      </c>
+      <c r="E88" s="22" t="n">
+        <v>58</v>
+      </c>
+      <c r="F88" s="22" t="n">
+        <v>593</v>
+      </c>
+      <c r="G88" s="22" t="n">
+        <v>24</v>
+      </c>
+      <c r="H88" s="22" t="n">
+        <v>589</v>
+      </c>
+      <c r="I88" s="22" t="n">
+        <v>73</v>
+      </c>
+      <c r="J88" s="22" t="n">
+        <v>613</v>
+      </c>
+      <c r="K88" s="22" t="n">
+        <v>34</v>
+      </c>
+      <c r="L88" s="22" t="n">
+        <v>654</v>
+      </c>
+      <c r="M88" s="22" t="n">
+        <v>75</v>
+      </c>
+      <c r="N88" s="22" t="n">
+        <v>732</v>
+      </c>
+      <c r="T88" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="D88" s="22" t="n">
-        <v>25</v>
-      </c>
-      <c r="E88" s="22" t="n">
-        <v>22</v>
-      </c>
-      <c r="F88" s="22" t="n">
+      <c r="U88" s="22" t="n">
+        <v>45</v>
+      </c>
+      <c r="V88" s="22" t="n">
+        <v>58</v>
+      </c>
+      <c r="W88" s="22" t="n">
+        <v>73</v>
+      </c>
+      <c r="X88" s="22" t="n">
         <v>75</v>
-      </c>
-      <c r="G88" s="22" t="n">
-        <v>74</v>
-      </c>
-      <c r="H88" s="22" t="n">
-        <v>75</v>
-      </c>
-      <c r="I88" s="22" t="n">
-        <v>42</v>
-      </c>
-      <c r="J88" s="22" t="n">
-        <v>47</v>
-      </c>
-      <c r="K88" s="22" t="n">
-        <v>40</v>
-      </c>
-      <c r="L88" s="22" t="n">
-        <v>67</v>
-      </c>
-      <c r="M88" s="22" t="n">
-        <v>50</v>
-      </c>
-      <c r="N88" s="22" t="n">
-        <v>53</v>
-      </c>
-      <c r="T88" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="U88" s="22" t="n">
-        <v>13</v>
-      </c>
-      <c r="V88" s="22" t="n">
-        <v>22</v>
-      </c>
-      <c r="W88" s="22" t="n">
-        <v>42</v>
-      </c>
-      <c r="X88" s="22" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>외환차손</t>
+          <t>외환차익</t>
         </is>
       </c>
       <c r="C89" s="22" t="n">
+        <v>-16</v>
+      </c>
+      <c r="D89" s="22" t="n">
+        <v>-183</v>
+      </c>
+      <c r="E89" s="22" t="n">
+        <v>306</v>
+      </c>
+      <c r="F89" s="22" t="n">
+        <v>365</v>
+      </c>
+      <c r="G89" s="22" t="n">
+        <v>-365</v>
+      </c>
+      <c r="H89" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D89" s="22" t="n">
+      <c r="I89" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E89" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" s="22" t="n">
-        <v>-15</v>
-      </c>
-      <c r="I89" s="22" t="n">
-        <v>75</v>
-      </c>
       <c r="J89" s="22" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="K89" s="22" t="n">
-        <v>0</v>
+        <v>-68</v>
       </c>
       <c r="L89" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" s="22" t="n">
-        <v>76</v>
+        <v>-8</v>
       </c>
       <c r="N89" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="T89" s="22" t="n">
-        <v>-5</v>
-      </c>
       <c r="U89" s="22" t="n">
-        <v>-155</v>
+        <v>0</v>
       </c>
       <c r="V89" s="22" t="n">
+        <v>306</v>
+      </c>
+      <c r="W89" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="W89" s="22" t="n">
-        <v>75</v>
-      </c>
-      <c r="X89" s="22" t="n">
-        <v>76</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>Rent Expenses On Real Estates NOE</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C90" s="22" t="n">
-        <v>25</v>
+        <v>151</v>
       </c>
       <c r="D90" s="22" t="n">
-        <v>18</v>
+        <v>126</v>
       </c>
       <c r="E90" s="22" t="n">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="F90" s="22" t="n">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="G90" s="22" t="n">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="H90" s="22" t="n">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="I90" s="22" t="n">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="J90" s="22" t="n">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="K90" s="22" t="n">
-        <v>20</v>
+        <v>123</v>
       </c>
       <c r="L90" s="22" t="n">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="M90" s="22" t="n">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="N90" s="22" t="n">
-        <v>18</v>
+        <v>97</v>
+      </c>
+      <c r="T90" s="22" t="n">
+        <v>30</v>
       </c>
       <c r="U90" s="22" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="V90" s="22" t="n">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="W90" s="22" t="n">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="X90" s="22" t="n">
-        <v>21</v>
+        <v>89</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>영업외수익 합계</t>
         </is>
       </c>
       <c r="C91" s="22" t="n">
-        <v>12</v>
+        <v>167</v>
       </c>
       <c r="D91" s="22" t="n">
-        <v>-2</v>
+        <v>460</v>
       </c>
       <c r="E91" s="22" t="n">
-        <v>9</v>
+        <v>482</v>
       </c>
       <c r="F91" s="22" t="n">
-        <v>3</v>
+        <v>1046</v>
       </c>
       <c r="G91" s="22" t="n">
-        <v>11</v>
+        <v>-219</v>
       </c>
       <c r="H91" s="22" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="I91" s="22" t="n">
-        <v>2</v>
+        <v>156</v>
       </c>
       <c r="J91" s="22" t="n">
-        <v>2</v>
+        <v>853</v>
       </c>
       <c r="K91" s="22" t="n">
-        <v>1</v>
+        <v>108</v>
       </c>
       <c r="L91" s="22" t="n">
-        <v>7</v>
+        <v>739</v>
       </c>
       <c r="M91" s="22" t="n">
-        <v>23</v>
+        <v>101</v>
       </c>
       <c r="N91" s="22" t="n">
-        <v>4</v>
+        <v>844</v>
       </c>
       <c r="T91" s="22" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="U91" s="22" t="n">
-        <v>-39</v>
+        <v>108</v>
       </c>
       <c r="V91" s="22" t="n">
-        <v>9</v>
+        <v>482</v>
       </c>
       <c r="W91" s="22" t="n">
-        <v>2</v>
+        <v>156</v>
       </c>
       <c r="X91" s="22" t="n">
-        <v>23</v>
+        <v>101</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="20" t="inlineStr">
         <is>
-          <t>영업외비용 합계</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="C92" s="22" t="n">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="D92" s="22" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E92" s="22" t="n">
+        <v>22</v>
+      </c>
+      <c r="F92" s="22" t="n">
+        <v>75</v>
+      </c>
+      <c r="G92" s="22" t="n">
+        <v>74</v>
+      </c>
+      <c r="H92" s="22" t="n">
+        <v>75</v>
+      </c>
+      <c r="I92" s="22" t="n">
+        <v>42</v>
+      </c>
+      <c r="J92" s="22" t="n">
+        <v>47</v>
+      </c>
+      <c r="K92" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="L92" s="22" t="n">
+        <v>67</v>
+      </c>
+      <c r="M92" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="F92" s="22" t="n">
-        <v>98</v>
-      </c>
-      <c r="G92" s="22" t="n">
-        <v>489</v>
-      </c>
-      <c r="H92" s="22" t="n">
-        <v>79</v>
-      </c>
-      <c r="I92" s="22" t="n">
-        <v>138</v>
-      </c>
-      <c r="J92" s="22" t="n">
-        <v>68</v>
-      </c>
-      <c r="K92" s="22" t="n">
-        <v>61</v>
-      </c>
-      <c r="L92" s="22" t="n">
-        <v>94</v>
-      </c>
-      <c r="M92" s="22" t="n">
-        <v>171</v>
-      </c>
       <c r="N92" s="22" t="n">
+        <v>53</v>
+      </c>
+      <c r="T92" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="U92" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="V92" s="22" t="n">
+        <v>22</v>
+      </c>
+      <c r="W92" s="22" t="n">
+        <v>42</v>
+      </c>
+      <c r="X92" s="22" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="20" t="inlineStr">
+        <is>
+          <t>외환차손</t>
+        </is>
+      </c>
+      <c r="C93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="22" t="n">
+        <v>-15</v>
+      </c>
+      <c r="I93" s="22" t="n">
+        <v>75</v>
+      </c>
+      <c r="J93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="22" t="n">
         <v>76</v>
       </c>
-      <c r="T92" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="U92" s="22" t="n">
-        <v>-140</v>
-      </c>
-      <c r="V92" s="22" t="n">
-        <v>50</v>
-      </c>
-      <c r="W92" s="22" t="n">
-        <v>138</v>
-      </c>
-      <c r="X92" s="22" t="n">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="9" t="inlineStr">
-        <is>
-          <t>경상이익</t>
-        </is>
-      </c>
-      <c r="C93" s="12" t="n">
-        <v>685</v>
-      </c>
-      <c r="D93" s="12" t="n">
-        <v>1341</v>
-      </c>
-      <c r="E93" s="12" t="n">
-        <v>1782</v>
-      </c>
-      <c r="F93" s="12" t="n">
-        <v>1005</v>
-      </c>
-      <c r="G93" s="12" t="n">
-        <v>65</v>
-      </c>
-      <c r="H93" s="12" t="n">
-        <v>1928</v>
-      </c>
-      <c r="I93" s="12" t="n">
-        <v>1557</v>
-      </c>
-      <c r="J93" s="12" t="n">
-        <v>687</v>
-      </c>
-      <c r="K93" s="12" t="n">
-        <v>805</v>
-      </c>
-      <c r="L93" s="12" t="n">
-        <v>1304</v>
-      </c>
-      <c r="M93" s="12" t="n">
-        <v>976</v>
-      </c>
-      <c r="N93" s="12" t="n">
-        <v>1574</v>
-      </c>
-      <c r="T93" s="12" t="n">
-        <v>2951</v>
-      </c>
-      <c r="U93" s="12" t="n">
-        <v>2549</v>
-      </c>
-      <c r="V93" s="12" t="n">
-        <v>1782</v>
-      </c>
-      <c r="W93" s="12" t="n">
-        <v>1557</v>
-      </c>
-      <c r="X93" s="12" t="n">
-        <v>976</v>
+      <c r="N93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" s="22" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U93" s="22" t="n">
+        <v>-155</v>
+      </c>
+      <c r="V93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" s="22" t="n">
+        <v>75</v>
+      </c>
+      <c r="X93" s="22" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각이익</t>
+          <t>Rent Expenses On Real Estates NOE</t>
         </is>
       </c>
       <c r="C94" s="22" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D94" s="22" t="n">
-        <v>1127</v>
+        <v>18</v>
       </c>
       <c r="E94" s="22" t="n">
-        <v>1218</v>
+        <v>19</v>
+      </c>
+      <c r="F94" s="22" t="n">
+        <v>19</v>
+      </c>
+      <c r="G94" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="H94" s="22" t="n">
+        <v>18</v>
       </c>
       <c r="I94" s="22" t="n">
-        <v>1100</v>
+        <v>19</v>
+      </c>
+      <c r="J94" s="22" t="n">
+        <v>18</v>
+      </c>
+      <c r="K94" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="L94" s="22" t="n">
+        <v>20</v>
       </c>
       <c r="M94" s="22" t="n">
-        <v>6671</v>
-      </c>
-      <c r="T94" s="22" t="n">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="N94" s="22" t="n">
+        <v>18</v>
       </c>
       <c r="U94" s="22" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="V94" s="22" t="n">
-        <v>1218</v>
+        <v>19</v>
       </c>
       <c r="W94" s="22" t="n">
-        <v>1100</v>
+        <v>19</v>
       </c>
       <c r="X94" s="22" t="n">
-        <v>6671</v>
+        <v>21</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="20" t="inlineStr">
         <is>
-          <t>특별이익 합계</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C95" s="22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D95" s="22" t="n">
-        <v>1127</v>
+        <v>-2</v>
       </c>
       <c r="E95" s="22" t="n">
-        <v>1218</v>
+        <v>9</v>
+      </c>
+      <c r="F95" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G95" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="H95" s="22" t="n">
+        <v>1</v>
       </c>
       <c r="I95" s="22" t="n">
-        <v>1100</v>
+        <v>2</v>
+      </c>
+      <c r="J95" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K95" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" s="22" t="n">
+        <v>7</v>
       </c>
       <c r="M95" s="22" t="n">
-        <v>6671</v>
+        <v>23</v>
+      </c>
+      <c r="N95" s="22" t="n">
+        <v>4</v>
       </c>
       <c r="T95" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U95" s="22" t="n">
-        <v>0</v>
+        <v>-39</v>
       </c>
       <c r="V95" s="22" t="n">
-        <v>1218</v>
+        <v>9</v>
       </c>
       <c r="W95" s="22" t="n">
-        <v>1100</v>
+        <v>2</v>
       </c>
       <c r="X95" s="22" t="n">
-        <v>6671</v>
+        <v>23</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각손실</t>
-        </is>
+          <t>영업외비용 합계</t>
+        </is>
+      </c>
+      <c r="C96" s="22" t="n">
+        <v>62</v>
       </c>
       <c r="D96" s="22" t="n">
+        <v>41</v>
+      </c>
+      <c r="E96" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="F96" s="22" t="n">
+        <v>98</v>
+      </c>
+      <c r="G96" s="22" t="n">
+        <v>489</v>
+      </c>
+      <c r="H96" s="22" t="n">
+        <v>79</v>
+      </c>
+      <c r="I96" s="22" t="n">
+        <v>138</v>
+      </c>
+      <c r="J96" s="22" t="n">
+        <v>68</v>
+      </c>
+      <c r="K96" s="22" t="n">
+        <v>61</v>
+      </c>
+      <c r="L96" s="22" t="n">
+        <v>94</v>
+      </c>
+      <c r="M96" s="22" t="n">
         <v>171</v>
       </c>
-      <c r="E96" s="22" t="n">
+      <c r="N96" s="22" t="n">
+        <v>76</v>
+      </c>
+      <c r="T96" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U96" s="22" t="n">
+        <v>-140</v>
+      </c>
+      <c r="V96" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="W96" s="22" t="n">
+        <v>138</v>
+      </c>
+      <c r="X96" s="22" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>경상이익</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="n">
+        <v>685</v>
+      </c>
+      <c r="D97" s="12" t="n">
+        <v>1341</v>
+      </c>
+      <c r="E97" s="12" t="n">
+        <v>1782</v>
+      </c>
+      <c r="F97" s="12" t="n">
+        <v>1005</v>
+      </c>
+      <c r="G97" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="H97" s="12" t="n">
+        <v>1928</v>
+      </c>
+      <c r="I97" s="12" t="n">
+        <v>1557</v>
+      </c>
+      <c r="J97" s="12" t="n">
+        <v>687</v>
+      </c>
+      <c r="K97" s="12" t="n">
+        <v>805</v>
+      </c>
+      <c r="L97" s="12" t="n">
+        <v>1304</v>
+      </c>
+      <c r="M97" s="12" t="n">
+        <v>976</v>
+      </c>
+      <c r="N97" s="12" t="n">
+        <v>1574</v>
+      </c>
+      <c r="T97" s="12" t="n">
+        <v>2951</v>
+      </c>
+      <c r="U97" s="12" t="n">
+        <v>2549</v>
+      </c>
+      <c r="V97" s="12" t="n">
+        <v>1782</v>
+      </c>
+      <c r="W97" s="12" t="n">
+        <v>1557</v>
+      </c>
+      <c r="X97" s="12" t="n">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G98" s="17">
+        <f>IF(OR(G97="",C97=""),"",IF(C97&lt;=0,"",IFERROR(G97/C97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H98" s="17">
+        <f>IF(OR(H97="",D97=""),"",IF(D97&lt;=0,"",IFERROR(H97/D97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I98" s="17">
+        <f>IF(OR(I97="",E97=""),"",IF(E97&lt;=0,"",IFERROR(I97/E97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J98" s="17">
+        <f>IF(OR(J97="",F97=""),"",IF(F97&lt;=0,"",IFERROR(J97/F97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K98" s="17">
+        <f>IF(OR(K97="",G97=""),"",IF(G97&lt;=0,"",IFERROR(K97/G97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L98" s="17">
+        <f>IF(OR(L97="",H97=""),"",IF(H97&lt;=0,"",IFERROR(L97/H97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M98" s="17">
+        <f>IF(OR(M97="",I97=""),"",IF(I97&lt;=0,"",IFERROR(M97/I97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N98" s="17">
+        <f>IF(OR(N97="",J97=""),"",IF(J97&lt;=0,"",IFERROR(N97/J97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T98" s="17">
+        <f>IF(OR(T97="",S97=""),"",IF(S97&lt;=0,"",IFERROR(T97/S97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U98" s="17">
+        <f>IF(OR(U97="",T97=""),"",IF(T97&lt;=0,"",IFERROR(U97/T97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V98" s="17">
+        <f>IF(OR(V97="",U97=""),"",IF(U97&lt;=0,"",IFERROR(V97/U97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W98" s="17">
+        <f>IF(OR(W97="",V97=""),"",IF(V97&lt;=0,"",IFERROR(W97/V97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X98" s="17">
+        <f>IF(OR(X97="",W97=""),"",IF(W97&lt;=0,"",IFERROR(X97/W97-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="20" t="inlineStr">
+        <is>
+          <t>투자유가증권 매각이익</t>
+        </is>
+      </c>
+      <c r="C99" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H96" s="22" t="n">
+      <c r="D99" s="22" t="n">
+        <v>1127</v>
+      </c>
+      <c r="E99" s="22" t="n">
+        <v>1218</v>
+      </c>
+      <c r="I99" s="22" t="n">
+        <v>1100</v>
+      </c>
+      <c r="M99" s="22" t="n">
+        <v>6671</v>
+      </c>
+      <c r="T99" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I96" s="22" t="n">
+      <c r="U99" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="U96" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V96" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W96" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="20" t="inlineStr">
-        <is>
-          <t>투자유가증권 매각손실</t>
-        </is>
-      </c>
-      <c r="C97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V97" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="20" t="inlineStr">
-        <is>
-          <t>특별손실 합계</t>
-        </is>
-      </c>
-      <c r="C98" s="22" t="n">
-        <v>16</v>
-      </c>
-      <c r="D98" s="22" t="n">
-        <v>171</v>
-      </c>
-      <c r="E98" s="22" t="n">
-        <v>608</v>
-      </c>
-      <c r="H98" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T98" s="22" t="n">
-        <v>1243</v>
-      </c>
-      <c r="U98" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V98" s="22" t="n">
-        <v>608</v>
-      </c>
-      <c r="W98" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="C99" s="12" t="n">
-        <v>668</v>
-      </c>
-      <c r="D99" s="12" t="n">
-        <v>2297</v>
-      </c>
-      <c r="E99" s="12" t="n">
-        <v>2393</v>
-      </c>
-      <c r="F99" s="12" t="n">
-        <v>1005</v>
-      </c>
-      <c r="G99" s="12" t="n">
-        <v>65</v>
-      </c>
-      <c r="H99" s="12" t="n">
-        <v>1928</v>
-      </c>
-      <c r="I99" s="12" t="n">
-        <v>2657</v>
-      </c>
-      <c r="J99" s="12" t="n">
-        <v>687</v>
-      </c>
-      <c r="K99" s="12" t="n">
-        <v>805</v>
-      </c>
-      <c r="L99" s="12" t="n">
-        <v>2633</v>
-      </c>
-      <c r="M99" s="12" t="n">
-        <v>6440</v>
-      </c>
-      <c r="N99" s="12" t="n">
-        <v>1574</v>
-      </c>
-      <c r="T99" s="12" t="n">
-        <v>1708</v>
-      </c>
-      <c r="U99" s="12" t="n">
-        <v>2549</v>
-      </c>
-      <c r="V99" s="12" t="n">
-        <v>2393</v>
-      </c>
-      <c r="W99" s="12" t="n">
-        <v>2657</v>
-      </c>
-      <c r="X99" s="12" t="n">
-        <v>6440</v>
+      <c r="V99" s="22" t="n">
+        <v>1218</v>
+      </c>
+      <c r="W99" s="22" t="n">
+        <v>1100</v>
+      </c>
+      <c r="X99" s="22" t="n">
+        <v>6671</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="20" t="inlineStr">
         <is>
-          <t>법인세·주민세·사업세</t>
+          <t>특별이익 합계</t>
         </is>
       </c>
       <c r="C100" s="22" t="n">
-        <v>629</v>
+        <v>0</v>
       </c>
       <c r="D100" s="22" t="n">
-        <v>656</v>
+        <v>1127</v>
       </c>
       <c r="E100" s="22" t="n">
-        <v>930</v>
-      </c>
-      <c r="F100" s="22" t="n">
-        <v>71</v>
-      </c>
-      <c r="G100" s="22" t="n">
-        <v>246</v>
-      </c>
-      <c r="H100" s="22" t="n">
-        <v>335</v>
+        <v>1218</v>
       </c>
       <c r="I100" s="22" t="n">
-        <v>797</v>
-      </c>
-      <c r="J100" s="22" t="n">
-        <v>115</v>
-      </c>
-      <c r="K100" s="22" t="n">
-        <v>404</v>
-      </c>
-      <c r="L100" s="22" t="n">
-        <v>590</v>
+        <v>1100</v>
       </c>
       <c r="M100" s="22" t="n">
-        <v>2271</v>
-      </c>
-      <c r="N100" s="22" t="n">
-        <v>121</v>
+        <v>6671</v>
       </c>
       <c r="T100" s="22" t="n">
-        <v>981</v>
+        <v>0</v>
       </c>
       <c r="U100" s="22" t="n">
-        <v>837</v>
+        <v>0</v>
       </c>
       <c r="V100" s="22" t="n">
-        <v>930</v>
+        <v>1218</v>
       </c>
       <c r="W100" s="22" t="n">
-        <v>797</v>
+        <v>1100</v>
       </c>
       <c r="X100" s="22" t="n">
-        <v>2271</v>
+        <v>6671</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="20" t="inlineStr">
         <is>
-          <t>법인세 조정액</t>
-        </is>
-      </c>
-      <c r="C101" s="22" t="n">
-        <v>-394</v>
+          <t>고정자산 제각손실</t>
+        </is>
       </c>
       <c r="D101" s="22" t="n">
-        <v>58</v>
+        <v>171</v>
       </c>
       <c r="E101" s="22" t="n">
-        <v>-252</v>
-      </c>
-      <c r="F101" s="22" t="n">
-        <v>208</v>
-      </c>
-      <c r="G101" s="22" t="n">
-        <v>-165</v>
+        <v>0</v>
       </c>
       <c r="H101" s="22" t="n">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="I101" s="22" t="n">
-        <v>-296</v>
-      </c>
-      <c r="J101" s="22" t="n">
-        <v>264</v>
-      </c>
-      <c r="K101" s="22" t="n">
-        <v>-223</v>
-      </c>
-      <c r="L101" s="22" t="n">
-        <v>132</v>
-      </c>
-      <c r="M101" s="22" t="n">
-        <v>-311</v>
-      </c>
-      <c r="N101" s="22" t="n">
-        <v>237</v>
-      </c>
-      <c r="T101" s="22" t="n">
-        <v>-331</v>
+        <v>0</v>
       </c>
       <c r="U101" s="22" t="n">
-        <v>-253</v>
+        <v>0</v>
       </c>
       <c r="V101" s="22" t="n">
-        <v>-252</v>
+        <v>0</v>
       </c>
       <c r="W101" s="22" t="n">
-        <v>-296</v>
-      </c>
-      <c r="X101" s="22" t="n">
-        <v>-311</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="20" t="inlineStr">
         <is>
-          <t>법인세 등 합계</t>
+          <t>투자유가증권 매각손실</t>
         </is>
       </c>
       <c r="C102" s="22" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="D102" s="22" t="n">
-        <v>715</v>
+        <v>0</v>
       </c>
       <c r="E102" s="22" t="n">
-        <v>678</v>
-      </c>
-      <c r="F102" s="22" t="n">
-        <v>280</v>
-      </c>
-      <c r="G102" s="22" t="n">
-        <v>80</v>
-      </c>
-      <c r="H102" s="22" t="n">
-        <v>644</v>
-      </c>
-      <c r="I102" s="22" t="n">
-        <v>502</v>
-      </c>
-      <c r="J102" s="22" t="n">
-        <v>379</v>
-      </c>
-      <c r="K102" s="22" t="n">
-        <v>182</v>
-      </c>
-      <c r="L102" s="22" t="n">
-        <v>722</v>
-      </c>
-      <c r="M102" s="22" t="n">
-        <v>1959</v>
-      </c>
-      <c r="N102" s="22" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="T102" s="22" t="n">
-        <v>648</v>
+        <v>0</v>
       </c>
       <c r="U102" s="22" t="n">
-        <v>584</v>
+        <v>0</v>
       </c>
       <c r="V102" s="22" t="n">
-        <v>678</v>
-      </c>
-      <c r="W102" s="22" t="n">
-        <v>502</v>
-      </c>
-      <c r="X102" s="22" t="n">
-        <v>1959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="9" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="C103" s="12" t="n">
-        <v>435</v>
-      </c>
-      <c r="D103" s="12" t="n">
-        <v>1582</v>
-      </c>
-      <c r="E103" s="12" t="n">
-        <v>1714</v>
-      </c>
-      <c r="F103" s="12" t="n">
-        <v>725</v>
-      </c>
-      <c r="G103" s="12" t="n">
-        <v>-16</v>
-      </c>
-      <c r="H103" s="12" t="n">
-        <v>1284</v>
-      </c>
-      <c r="I103" s="12" t="n">
-        <v>2155</v>
-      </c>
-      <c r="J103" s="12" t="n">
-        <v>307</v>
-      </c>
-      <c r="K103" s="12" t="n">
-        <v>623</v>
-      </c>
-      <c r="L103" s="12" t="n">
-        <v>1912</v>
-      </c>
-      <c r="M103" s="12" t="n">
-        <v>4481</v>
-      </c>
-      <c r="N103" s="12" t="n">
-        <v>1215</v>
-      </c>
-      <c r="T103" s="12" t="n">
-        <v>1059</v>
-      </c>
-      <c r="U103" s="12" t="n">
-        <v>1964</v>
-      </c>
-      <c r="V103" s="12" t="n">
-        <v>1714</v>
-      </c>
-      <c r="W103" s="12" t="n">
-        <v>2155</v>
-      </c>
-      <c r="X103" s="12" t="n">
-        <v>4481</v>
+      <c r="A103" s="20" t="inlineStr">
+        <is>
+          <t>특별손실 합계</t>
+        </is>
+      </c>
+      <c r="C103" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="D103" s="22" t="n">
+        <v>171</v>
+      </c>
+      <c r="E103" s="22" t="n">
+        <v>608</v>
+      </c>
+      <c r="H103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" s="22" t="n">
+        <v>1243</v>
+      </c>
+      <c r="U103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V103" s="22" t="n">
+        <v>608</v>
+      </c>
+      <c r="W103" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>지배주주 순이익</t>
+          <t>법인세차감전 순이익</t>
         </is>
       </c>
       <c r="C104" s="12" t="n">
-        <v>435</v>
+        <v>668</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1582</v>
+        <v>2297</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1714</v>
+        <v>2393</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>725</v>
+        <v>1005</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>-16</v>
+        <v>65</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1284</v>
+        <v>1928</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>2155</v>
+        <v>2657</v>
       </c>
       <c r="J104" s="12" t="n">
-        <v>307</v>
+        <v>687</v>
       </c>
       <c r="K104" s="12" t="n">
-        <v>623</v>
+        <v>805</v>
       </c>
       <c r="L104" s="12" t="n">
-        <v>1912</v>
+        <v>2633</v>
       </c>
       <c r="M104" s="12" t="n">
-        <v>4481</v>
+        <v>6440</v>
       </c>
       <c r="N104" s="12" t="n">
-        <v>1215</v>
+        <v>1574</v>
       </c>
       <c r="T104" s="12" t="n">
-        <v>1059</v>
+        <v>1708</v>
       </c>
       <c r="U104" s="12" t="n">
-        <v>1964</v>
+        <v>2549</v>
       </c>
       <c r="V104" s="12" t="n">
-        <v>1714</v>
+        <v>2393</v>
       </c>
       <c r="W104" s="12" t="n">
-        <v>2155</v>
+        <v>2657</v>
       </c>
       <c r="X104" s="12" t="n">
-        <v>4481</v>
+        <v>6440</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="20" t="inlineStr">
+        <is>
+          <t>법인세·주민세·사업세</t>
+        </is>
+      </c>
+      <c r="C105" s="22" t="n">
+        <v>629</v>
+      </c>
+      <c r="D105" s="22" t="n">
+        <v>656</v>
+      </c>
+      <c r="E105" s="22" t="n">
+        <v>930</v>
+      </c>
+      <c r="F105" s="22" t="n">
+        <v>71</v>
+      </c>
+      <c r="G105" s="22" t="n">
+        <v>246</v>
+      </c>
+      <c r="H105" s="22" t="n">
+        <v>335</v>
+      </c>
+      <c r="I105" s="22" t="n">
+        <v>797</v>
+      </c>
+      <c r="J105" s="22" t="n">
+        <v>115</v>
+      </c>
+      <c r="K105" s="22" t="n">
+        <v>404</v>
+      </c>
+      <c r="L105" s="22" t="n">
+        <v>590</v>
+      </c>
+      <c r="M105" s="22" t="n">
+        <v>2271</v>
+      </c>
+      <c r="N105" s="22" t="n">
+        <v>121</v>
+      </c>
+      <c r="T105" s="22" t="n">
+        <v>981</v>
+      </c>
+      <c r="U105" s="22" t="n">
+        <v>837</v>
+      </c>
+      <c r="V105" s="22" t="n">
+        <v>930</v>
+      </c>
+      <c r="W105" s="22" t="n">
+        <v>797</v>
+      </c>
+      <c r="X105" s="22" t="n">
+        <v>2271</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="18" t="inlineStr">
-        <is>
-          <t>포괄손익 · 전 항목</t>
-        </is>
-      </c>
-      <c r="B106" s="44" t="inlineStr">
-        <is>
-          <t>분기 = 3개월 단독</t>
-        </is>
-      </c>
-      <c r="C106" s="18" t="n"/>
-      <c r="D106" s="18" t="n"/>
-      <c r="E106" s="18" t="n"/>
-      <c r="F106" s="18" t="n"/>
-      <c r="G106" s="18" t="n"/>
-      <c r="H106" s="18" t="n"/>
-      <c r="I106" s="18" t="n"/>
-      <c r="J106" s="18" t="n"/>
-      <c r="K106" s="18" t="n"/>
-      <c r="L106" s="18" t="n"/>
-      <c r="M106" s="18" t="n"/>
-      <c r="N106" s="18" t="n"/>
-      <c r="O106" s="18" t="n"/>
-      <c r="P106" s="18" t="n"/>
-      <c r="Q106" s="18" t="n"/>
-      <c r="R106" s="18" t="n"/>
-      <c r="S106" s="18" t="n"/>
-      <c r="T106" s="18" t="n"/>
-      <c r="U106" s="18" t="n"/>
-      <c r="V106" s="18" t="n"/>
-      <c r="W106" s="18" t="n"/>
-      <c r="X106" s="18" t="n"/>
-      <c r="Y106" s="18" t="n"/>
-      <c r="Z106" s="18" t="n"/>
-      <c r="AA106" s="18" t="n"/>
-      <c r="AB106" s="18" t="n"/>
-      <c r="AC106" s="18" t="n"/>
+      <c r="A106" s="20" t="inlineStr">
+        <is>
+          <t>법인세 조정액</t>
+        </is>
+      </c>
+      <c r="C106" s="22" t="n">
+        <v>-394</v>
+      </c>
+      <c r="D106" s="22" t="n">
+        <v>58</v>
+      </c>
+      <c r="E106" s="22" t="n">
+        <v>-252</v>
+      </c>
+      <c r="F106" s="22" t="n">
+        <v>208</v>
+      </c>
+      <c r="G106" s="22" t="n">
+        <v>-165</v>
+      </c>
+      <c r="H106" s="22" t="n">
+        <v>309</v>
+      </c>
+      <c r="I106" s="22" t="n">
+        <v>-296</v>
+      </c>
+      <c r="J106" s="22" t="n">
+        <v>264</v>
+      </c>
+      <c r="K106" s="22" t="n">
+        <v>-223</v>
+      </c>
+      <c r="L106" s="22" t="n">
+        <v>132</v>
+      </c>
+      <c r="M106" s="22" t="n">
+        <v>-311</v>
+      </c>
+      <c r="N106" s="22" t="n">
+        <v>237</v>
+      </c>
+      <c r="T106" s="22" t="n">
+        <v>-331</v>
+      </c>
+      <c r="U106" s="22" t="n">
+        <v>-253</v>
+      </c>
+      <c r="V106" s="22" t="n">
+        <v>-252</v>
+      </c>
+      <c r="W106" s="22" t="n">
+        <v>-296</v>
+      </c>
+      <c r="X106" s="22" t="n">
+        <v>-311</v>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B107" s="5" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="C107" s="5" t="inlineStr">
-        <is>
-          <t>2024.2Q</t>
-        </is>
-      </c>
-      <c r="D107" s="5" t="inlineStr">
-        <is>
-          <t>2024.3Q</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>2024.4Q</t>
-        </is>
-      </c>
-      <c r="F107" s="5" t="inlineStr">
-        <is>
-          <t>2025.1Q</t>
-        </is>
-      </c>
-      <c r="G107" s="5" t="inlineStr">
-        <is>
-          <t>2025.2Q</t>
-        </is>
-      </c>
-      <c r="H107" s="5" t="inlineStr">
-        <is>
-          <t>2025.3Q</t>
-        </is>
-      </c>
-      <c r="I107" s="5" t="inlineStr">
-        <is>
-          <t>2025.4Q</t>
-        </is>
-      </c>
-      <c r="J107" s="5" t="inlineStr">
-        <is>
-          <t>2026.1Q</t>
-        </is>
-      </c>
-      <c r="K107" s="5" t="inlineStr">
-        <is>
-          <t>2026.2Q</t>
-        </is>
-      </c>
-      <c r="L107" s="5" t="inlineStr">
-        <is>
-          <t>2026.3Q</t>
-        </is>
-      </c>
-      <c r="M107" s="5" t="inlineStr">
-        <is>
-          <t>2026.4Q</t>
-        </is>
-      </c>
-      <c r="N107" s="5" t="inlineStr">
-        <is>
-          <t>2027.1Q</t>
-        </is>
-      </c>
-      <c r="O107" s="5" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="P107" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="Q107" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="R107" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="S107" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="T107" s="5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="U107" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V107" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="W107" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="X107" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Y107" s="5" t="inlineStr">
-        <is>
-          <t>2027(MW)</t>
-        </is>
-      </c>
-      <c r="Z107" s="5" t="inlineStr">
-        <is>
-          <t>2028(MW)</t>
-        </is>
-      </c>
-      <c r="AA107" s="5" t="inlineStr">
-        <is>
-          <t>2029(MW)</t>
-        </is>
-      </c>
-      <c r="AB107" s="5" t="inlineStr">
-        <is>
-          <t>2030(MW)</t>
-        </is>
-      </c>
-      <c r="AC107" s="5" t="inlineStr">
-        <is>
-          <t>2031(MW)</t>
-        </is>
+      <c r="A107" s="20" t="inlineStr">
+        <is>
+          <t>법인세 등 합계</t>
+        </is>
+      </c>
+      <c r="C107" s="22" t="n">
+        <v>234</v>
+      </c>
+      <c r="D107" s="22" t="n">
+        <v>715</v>
+      </c>
+      <c r="E107" s="22" t="n">
+        <v>678</v>
+      </c>
+      <c r="F107" s="22" t="n">
+        <v>280</v>
+      </c>
+      <c r="G107" s="22" t="n">
+        <v>80</v>
+      </c>
+      <c r="H107" s="22" t="n">
+        <v>644</v>
+      </c>
+      <c r="I107" s="22" t="n">
+        <v>502</v>
+      </c>
+      <c r="J107" s="22" t="n">
+        <v>379</v>
+      </c>
+      <c r="K107" s="22" t="n">
+        <v>182</v>
+      </c>
+      <c r="L107" s="22" t="n">
+        <v>722</v>
+      </c>
+      <c r="M107" s="22" t="n">
+        <v>1959</v>
+      </c>
+      <c r="N107" s="22" t="n">
+        <v>359</v>
+      </c>
+      <c r="T107" s="22" t="n">
+        <v>648</v>
+      </c>
+      <c r="U107" s="22" t="n">
+        <v>584</v>
+      </c>
+      <c r="V107" s="22" t="n">
+        <v>678</v>
+      </c>
+      <c r="W107" s="22" t="n">
+        <v>502</v>
+      </c>
+      <c r="X107" s="22" t="n">
+        <v>1959</v>
       </c>
     </row>
     <row r="108">
@@ -7399,2847 +7440,3277 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="20" t="inlineStr">
-        <is>
-          <t>기타유가증권 평가차액</t>
-        </is>
-      </c>
-      <c r="C109" s="22" t="n">
-        <v>288</v>
-      </c>
-      <c r="D109" s="22" t="n">
-        <v>1640</v>
-      </c>
-      <c r="E109" s="22" t="n">
-        <v>-65</v>
-      </c>
-      <c r="F109" s="22" t="n">
-        <v>4706</v>
-      </c>
-      <c r="G109" s="22" t="n">
-        <v>-4965</v>
-      </c>
-      <c r="H109" s="22" t="n">
-        <v>-1059</v>
-      </c>
-      <c r="I109" s="22" t="n">
-        <v>-3540</v>
-      </c>
-      <c r="J109" s="22" t="n">
-        <v>-104</v>
-      </c>
-      <c r="K109" s="22" t="n">
-        <v>8005</v>
-      </c>
-      <c r="L109" s="22" t="n">
-        <v>5067</v>
-      </c>
-      <c r="M109" s="22" t="n">
-        <v>-2395</v>
-      </c>
-      <c r="N109" s="22" t="n">
-        <v>63923</v>
-      </c>
-      <c r="T109" s="22" t="n">
-        <v>-4312</v>
-      </c>
-      <c r="U109" s="22" t="n">
-        <v>4485</v>
-      </c>
-      <c r="V109" s="22" t="n">
-        <v>-65</v>
-      </c>
-      <c r="W109" s="22" t="n">
-        <v>-3540</v>
-      </c>
-      <c r="X109" s="22" t="n">
-        <v>-2395</v>
+      <c r="A109" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G109" s="17">
+        <f>IF(OR(G108="",C108=""),"",IF(C108&lt;=0,"",IFERROR(G108/C108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H109" s="17">
+        <f>IF(OR(H108="",D108=""),"",IF(D108&lt;=0,"",IFERROR(H108/D108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I109" s="17">
+        <f>IF(OR(I108="",E108=""),"",IF(E108&lt;=0,"",IFERROR(I108/E108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J109" s="17">
+        <f>IF(OR(J108="",F108=""),"",IF(F108&lt;=0,"",IFERROR(J108/F108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K109" s="17">
+        <f>IF(OR(K108="",G108=""),"",IF(G108&lt;=0,"",IFERROR(K108/G108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L109" s="17">
+        <f>IF(OR(L108="",H108=""),"",IF(H108&lt;=0,"",IFERROR(L108/H108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M109" s="17">
+        <f>IF(OR(M108="",I108=""),"",IF(I108&lt;=0,"",IFERROR(M108/I108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N109" s="17">
+        <f>IF(OR(N108="",J108=""),"",IF(J108&lt;=0,"",IFERROR(N108/J108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T109" s="17">
+        <f>IF(OR(T108="",S108=""),"",IF(S108&lt;=0,"",IFERROR(T108/S108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U109" s="17">
+        <f>IF(OR(U108="",T108=""),"",IF(T108&lt;=0,"",IFERROR(U108/T108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V109" s="17">
+        <f>IF(OR(V108="",U108=""),"",IF(U108&lt;=0,"",IFERROR(V108/U108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W109" s="17">
+        <f>IF(OR(W108="",V108=""),"",IF(V108&lt;=0,"",IFERROR(W108/V108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X109" s="17">
+        <f>IF(OR(X108="",W108=""),"",IF(W108&lt;=0,"",IFERROR(X108/W108-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="20" t="inlineStr">
-        <is>
-          <t>해외사업환산조정</t>
-        </is>
-      </c>
-      <c r="C110" s="22" t="n">
-        <v>328</v>
-      </c>
-      <c r="D110" s="22" t="n">
-        <v>-459</v>
-      </c>
-      <c r="E110" s="22" t="n">
-        <v>993</v>
-      </c>
-      <c r="F110" s="22" t="n">
-        <v>1431</v>
-      </c>
-      <c r="G110" s="22" t="n">
-        <v>-2114</v>
-      </c>
-      <c r="H110" s="22" t="n">
-        <v>1468</v>
-      </c>
-      <c r="I110" s="22" t="n">
-        <v>-953</v>
-      </c>
-      <c r="J110" s="22" t="n">
-        <v>215</v>
-      </c>
-      <c r="K110" s="22" t="n">
-        <v>707</v>
-      </c>
-      <c r="L110" s="22" t="n">
-        <v>1549</v>
-      </c>
-      <c r="M110" s="22" t="n">
-        <v>207</v>
-      </c>
-      <c r="N110" s="22" t="n">
-        <v>512</v>
-      </c>
-      <c r="T110" s="22" t="n">
-        <v>956</v>
-      </c>
-      <c r="U110" s="22" t="n">
-        <v>410</v>
-      </c>
-      <c r="V110" s="22" t="n">
-        <v>993</v>
-      </c>
-      <c r="W110" s="22" t="n">
-        <v>-953</v>
-      </c>
-      <c r="X110" s="22" t="n">
-        <v>207</v>
+      <c r="A110" s="9" t="inlineStr">
+        <is>
+          <t>지배주주 순이익</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="n">
+        <v>435</v>
+      </c>
+      <c r="D110" s="12" t="n">
+        <v>1582</v>
+      </c>
+      <c r="E110" s="12" t="n">
+        <v>1714</v>
+      </c>
+      <c r="F110" s="12" t="n">
+        <v>725</v>
+      </c>
+      <c r="G110" s="12" t="n">
+        <v>-16</v>
+      </c>
+      <c r="H110" s="12" t="n">
+        <v>1284</v>
+      </c>
+      <c r="I110" s="12" t="n">
+        <v>2155</v>
+      </c>
+      <c r="J110" s="12" t="n">
+        <v>307</v>
+      </c>
+      <c r="K110" s="12" t="n">
+        <v>623</v>
+      </c>
+      <c r="L110" s="12" t="n">
+        <v>1912</v>
+      </c>
+      <c r="M110" s="12" t="n">
+        <v>4481</v>
+      </c>
+      <c r="N110" s="12" t="n">
+        <v>1215</v>
+      </c>
+      <c r="T110" s="12" t="n">
+        <v>1059</v>
+      </c>
+      <c r="U110" s="12" t="n">
+        <v>1964</v>
+      </c>
+      <c r="V110" s="12" t="n">
+        <v>1714</v>
+      </c>
+      <c r="W110" s="12" t="n">
+        <v>2155</v>
+      </c>
+      <c r="X110" s="12" t="n">
+        <v>4481</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="20" t="inlineStr">
-        <is>
-          <t>퇴직급여 조정액</t>
-        </is>
-      </c>
-      <c r="C111" s="22" t="n">
-        <v>-37</v>
-      </c>
-      <c r="D111" s="22" t="n">
-        <v>-36</v>
-      </c>
-      <c r="E111" s="22" t="n">
-        <v>281</v>
-      </c>
-      <c r="F111" s="22" t="n">
-        <v>-52</v>
-      </c>
-      <c r="G111" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="H111" s="22" t="n">
-        <v>-42</v>
-      </c>
-      <c r="I111" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="J111" s="22" t="n">
-        <v>-44</v>
-      </c>
-      <c r="K111" s="22" t="n">
-        <v>-122</v>
-      </c>
-      <c r="L111" s="22" t="n">
-        <v>-68</v>
-      </c>
-      <c r="M111" s="22" t="n">
-        <v>227</v>
-      </c>
-      <c r="N111" s="22" t="n">
-        <v>-117</v>
-      </c>
-      <c r="T111" s="22" t="n">
-        <v>137</v>
-      </c>
-      <c r="U111" s="22" t="n">
-        <v>358</v>
-      </c>
-      <c r="V111" s="22" t="n">
-        <v>281</v>
-      </c>
-      <c r="W111" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="X111" s="22" t="n">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="20" t="inlineStr">
-        <is>
-          <t>기타포괄손익 합계</t>
-        </is>
-      </c>
-      <c r="C112" s="22" t="n">
-        <v>579</v>
-      </c>
-      <c r="D112" s="22" t="n">
-        <v>1145</v>
-      </c>
-      <c r="E112" s="22" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F112" s="22" t="n">
-        <v>6085</v>
-      </c>
-      <c r="G112" s="22" t="n">
-        <v>-7075</v>
-      </c>
-      <c r="H112" s="22" t="n">
-        <v>368</v>
-      </c>
-      <c r="I112" s="22" t="n">
-        <v>-4392</v>
-      </c>
-      <c r="J112" s="22" t="n">
-        <v>66</v>
-      </c>
-      <c r="K112" s="22" t="n">
-        <v>8591</v>
-      </c>
-      <c r="L112" s="22" t="n">
-        <v>6547</v>
-      </c>
-      <c r="M112" s="22" t="n">
-        <v>-1960</v>
-      </c>
-      <c r="N112" s="22" t="n">
-        <v>64318</v>
-      </c>
-      <c r="T112" s="22" t="n">
-        <v>-3218</v>
-      </c>
-      <c r="U112" s="22" t="n">
-        <v>5255</v>
-      </c>
-      <c r="V112" s="22" t="n">
-        <v>1209</v>
-      </c>
-      <c r="W112" s="22" t="n">
-        <v>-4392</v>
-      </c>
-      <c r="X112" s="22" t="n">
-        <v>-1960</v>
+      <c r="A111" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G111" s="17">
+        <f>IF(OR(G110="",C110=""),"",IF(C110&lt;=0,"",IFERROR(G110/C110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H111" s="17">
+        <f>IF(OR(H110="",D110=""),"",IF(D110&lt;=0,"",IFERROR(H110/D110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I111" s="17">
+        <f>IF(OR(I110="",E110=""),"",IF(E110&lt;=0,"",IFERROR(I110/E110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J111" s="17">
+        <f>IF(OR(J110="",F110=""),"",IF(F110&lt;=0,"",IFERROR(J110/F110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K111" s="17">
+        <f>IF(OR(K110="",G110=""),"",IF(G110&lt;=0,"",IFERROR(K110/G110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L111" s="17">
+        <f>IF(OR(L110="",H110=""),"",IF(H110&lt;=0,"",IFERROR(L110/H110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M111" s="17">
+        <f>IF(OR(M110="",I110=""),"",IF(I110&lt;=0,"",IFERROR(M110/I110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N111" s="17">
+        <f>IF(OR(N110="",J110=""),"",IF(J110&lt;=0,"",IFERROR(N110/J110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T111" s="17">
+        <f>IF(OR(T110="",S110=""),"",IF(S110&lt;=0,"",IFERROR(T110/S110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U111" s="17">
+        <f>IF(OR(U110="",T110=""),"",IF(T110&lt;=0,"",IFERROR(U110/T110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V111" s="17">
+        <f>IF(OR(V110="",U110=""),"",IF(U110&lt;=0,"",IFERROR(V110/U110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W111" s="17">
+        <f>IF(OR(W110="",V110=""),"",IF(V110&lt;=0,"",IFERROR(W110/V110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X111" s="17">
+        <f>IF(OR(X110="",W110=""),"",IF(W110&lt;=0,"",IFERROR(X110/W110-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="9" t="inlineStr">
-        <is>
-          <t>포괄이익</t>
-        </is>
-      </c>
-      <c r="C113" s="12" t="n">
-        <v>1013</v>
-      </c>
-      <c r="D113" s="12" t="n">
-        <v>2727</v>
-      </c>
-      <c r="E113" s="12" t="n">
-        <v>2924</v>
-      </c>
-      <c r="F113" s="12" t="n">
-        <v>6811</v>
-      </c>
-      <c r="G113" s="12" t="n">
-        <v>-7092</v>
-      </c>
-      <c r="H113" s="12" t="n">
-        <v>1651</v>
-      </c>
-      <c r="I113" s="12" t="n">
-        <v>-2236</v>
-      </c>
-      <c r="J113" s="12" t="n">
-        <v>374</v>
-      </c>
-      <c r="K113" s="12" t="n">
-        <v>9213</v>
-      </c>
-      <c r="L113" s="12" t="n">
-        <v>8459</v>
-      </c>
-      <c r="M113" s="12" t="n">
-        <v>2522</v>
-      </c>
-      <c r="N113" s="12" t="n">
-        <v>65533</v>
-      </c>
-      <c r="T113" s="12" t="n">
-        <v>-2160</v>
-      </c>
-      <c r="U113" s="12" t="n">
-        <v>7219</v>
-      </c>
-      <c r="V113" s="12" t="n">
-        <v>2924</v>
-      </c>
-      <c r="W113" s="12" t="n">
-        <v>-2236</v>
-      </c>
-      <c r="X113" s="12" t="n">
-        <v>2522</v>
-      </c>
+      <c r="A113" s="18" t="inlineStr">
+        <is>
+          <t>포괄손익 · 전 항목</t>
+        </is>
+      </c>
+      <c r="B113" s="44" t="inlineStr">
+        <is>
+          <t>분기 = 3개월 단독</t>
+        </is>
+      </c>
+      <c r="C113" s="18" t="n"/>
+      <c r="D113" s="18" t="n"/>
+      <c r="E113" s="18" t="n"/>
+      <c r="F113" s="18" t="n"/>
+      <c r="G113" s="18" t="n"/>
+      <c r="H113" s="18" t="n"/>
+      <c r="I113" s="18" t="n"/>
+      <c r="J113" s="18" t="n"/>
+      <c r="K113" s="18" t="n"/>
+      <c r="L113" s="18" t="n"/>
+      <c r="M113" s="18" t="n"/>
+      <c r="N113" s="18" t="n"/>
+      <c r="O113" s="18" t="n"/>
+      <c r="P113" s="18" t="n"/>
+      <c r="Q113" s="18" t="n"/>
+      <c r="R113" s="18" t="n"/>
+      <c r="S113" s="18" t="n"/>
+      <c r="T113" s="18" t="n"/>
+      <c r="U113" s="18" t="n"/>
+      <c r="V113" s="18" t="n"/>
+      <c r="W113" s="18" t="n"/>
+      <c r="X113" s="18" t="n"/>
+      <c r="Y113" s="18" t="n"/>
+      <c r="Z113" s="18" t="n"/>
+      <c r="AA113" s="18" t="n"/>
+      <c r="AB113" s="18" t="n"/>
+      <c r="AC113" s="18" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="9" t="inlineStr">
-        <is>
-          <t>지배주주 포괄이익</t>
-        </is>
-      </c>
-      <c r="C114" s="12" t="n">
-        <v>1013</v>
-      </c>
-      <c r="D114" s="12" t="n">
-        <v>2727</v>
-      </c>
-      <c r="E114" s="12" t="n">
-        <v>2924</v>
-      </c>
-      <c r="F114" s="12" t="n">
-        <v>6811</v>
-      </c>
-      <c r="G114" s="12" t="n">
-        <v>-7092</v>
-      </c>
-      <c r="H114" s="12" t="n">
-        <v>1651</v>
-      </c>
-      <c r="I114" s="12" t="n">
-        <v>-2236</v>
-      </c>
-      <c r="J114" s="12" t="n">
-        <v>374</v>
-      </c>
-      <c r="K114" s="12" t="n">
-        <v>9213</v>
-      </c>
-      <c r="L114" s="12" t="n">
-        <v>8459</v>
-      </c>
-      <c r="M114" s="12" t="n">
-        <v>2522</v>
-      </c>
-      <c r="N114" s="12" t="n">
-        <v>65533</v>
-      </c>
-      <c r="T114" s="12" t="n">
-        <v>-2160</v>
-      </c>
-      <c r="U114" s="12" t="n">
-        <v>7219</v>
-      </c>
-      <c r="V114" s="12" t="n">
-        <v>2924</v>
-      </c>
-      <c r="W114" s="12" t="n">
-        <v>-2236</v>
-      </c>
-      <c r="X114" s="12" t="n">
-        <v>2522</v>
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>2024.2Q</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>2024.3Q</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>2024.4Q</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>2025.1Q</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>2025.2Q</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="inlineStr">
+        <is>
+          <t>2025.3Q</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>2025.4Q</t>
+        </is>
+      </c>
+      <c r="J114" s="5" t="inlineStr">
+        <is>
+          <t>2026.1Q</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="inlineStr">
+        <is>
+          <t>2026.2Q</t>
+        </is>
+      </c>
+      <c r="L114" s="5" t="inlineStr">
+        <is>
+          <t>2026.3Q</t>
+        </is>
+      </c>
+      <c r="M114" s="5" t="inlineStr">
+        <is>
+          <t>2026.4Q</t>
+        </is>
+      </c>
+      <c r="N114" s="5" t="inlineStr">
+        <is>
+          <t>2027.1Q</t>
+        </is>
+      </c>
+      <c r="O114" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="P114" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q114" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="R114" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="S114" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="T114" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U114" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V114" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="W114" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="X114" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y114" s="5" t="inlineStr">
+        <is>
+          <t>2027(MW)</t>
+        </is>
+      </c>
+      <c r="Z114" s="5" t="inlineStr">
+        <is>
+          <t>2028(MW)</t>
+        </is>
+      </c>
+      <c r="AA114" s="5" t="inlineStr">
+        <is>
+          <t>2029(MW)</t>
+        </is>
+      </c>
+      <c r="AB114" s="5" t="inlineStr">
+        <is>
+          <t>2030(MW)</t>
+        </is>
+      </c>
+      <c r="AC114" s="5" t="inlineStr">
+        <is>
+          <t>2031(MW)</t>
+        </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="n">
+        <v>435</v>
+      </c>
+      <c r="D115" s="12" t="n">
+        <v>1582</v>
+      </c>
+      <c r="E115" s="12" t="n">
+        <v>1714</v>
+      </c>
+      <c r="F115" s="12" t="n">
+        <v>725</v>
+      </c>
+      <c r="G115" s="12" t="n">
+        <v>-16</v>
+      </c>
+      <c r="H115" s="12" t="n">
+        <v>1284</v>
+      </c>
+      <c r="I115" s="12" t="n">
+        <v>2155</v>
+      </c>
+      <c r="J115" s="12" t="n">
+        <v>307</v>
+      </c>
+      <c r="K115" s="12" t="n">
+        <v>623</v>
+      </c>
+      <c r="L115" s="12" t="n">
+        <v>1912</v>
+      </c>
+      <c r="M115" s="12" t="n">
+        <v>4481</v>
+      </c>
+      <c r="N115" s="12" t="n">
+        <v>1215</v>
+      </c>
+      <c r="T115" s="12" t="n">
+        <v>1059</v>
+      </c>
+      <c r="U115" s="12" t="n">
+        <v>1964</v>
+      </c>
+      <c r="V115" s="12" t="n">
+        <v>1714</v>
+      </c>
+      <c r="W115" s="12" t="n">
+        <v>2155</v>
+      </c>
+      <c r="X115" s="12" t="n">
+        <v>4481</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="20" t="inlineStr">
+        <is>
+          <t>기타유가증권 평가차액</t>
+        </is>
+      </c>
+      <c r="C116" s="22" t="n">
+        <v>288</v>
+      </c>
+      <c r="D116" s="22" t="n">
+        <v>1640</v>
+      </c>
+      <c r="E116" s="22" t="n">
+        <v>-65</v>
+      </c>
+      <c r="F116" s="22" t="n">
+        <v>4706</v>
+      </c>
+      <c r="G116" s="22" t="n">
+        <v>-4965</v>
+      </c>
+      <c r="H116" s="22" t="n">
+        <v>-1059</v>
+      </c>
+      <c r="I116" s="22" t="n">
+        <v>-3540</v>
+      </c>
+      <c r="J116" s="22" t="n">
+        <v>-104</v>
+      </c>
+      <c r="K116" s="22" t="n">
+        <v>8005</v>
+      </c>
+      <c r="L116" s="22" t="n">
+        <v>5067</v>
+      </c>
+      <c r="M116" s="22" t="n">
+        <v>-2395</v>
+      </c>
+      <c r="N116" s="22" t="n">
+        <v>63923</v>
+      </c>
+      <c r="T116" s="22" t="n">
+        <v>-4312</v>
+      </c>
+      <c r="U116" s="22" t="n">
+        <v>4485</v>
+      </c>
+      <c r="V116" s="22" t="n">
+        <v>-65</v>
+      </c>
+      <c r="W116" s="22" t="n">
+        <v>-3540</v>
+      </c>
+      <c r="X116" s="22" t="n">
+        <v>-2395</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="20" t="inlineStr">
+        <is>
+          <t>해외사업환산조정</t>
+        </is>
+      </c>
+      <c r="C117" s="22" t="n">
+        <v>328</v>
+      </c>
+      <c r="D117" s="22" t="n">
+        <v>-459</v>
+      </c>
+      <c r="E117" s="22" t="n">
+        <v>993</v>
+      </c>
+      <c r="F117" s="22" t="n">
+        <v>1431</v>
+      </c>
+      <c r="G117" s="22" t="n">
+        <v>-2114</v>
+      </c>
+      <c r="H117" s="22" t="n">
+        <v>1468</v>
+      </c>
+      <c r="I117" s="22" t="n">
+        <v>-953</v>
+      </c>
+      <c r="J117" s="22" t="n">
+        <v>215</v>
+      </c>
+      <c r="K117" s="22" t="n">
+        <v>707</v>
+      </c>
+      <c r="L117" s="22" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M117" s="22" t="n">
+        <v>207</v>
+      </c>
+      <c r="N117" s="22" t="n">
+        <v>512</v>
+      </c>
+      <c r="T117" s="22" t="n">
+        <v>956</v>
+      </c>
+      <c r="U117" s="22" t="n">
+        <v>410</v>
+      </c>
+      <c r="V117" s="22" t="n">
+        <v>993</v>
+      </c>
+      <c r="W117" s="22" t="n">
+        <v>-953</v>
+      </c>
+      <c r="X117" s="22" t="n">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="20" t="inlineStr">
+        <is>
+          <t>퇴직급여 조정액</t>
+        </is>
+      </c>
+      <c r="C118" s="22" t="n">
+        <v>-37</v>
+      </c>
+      <c r="D118" s="22" t="n">
+        <v>-36</v>
+      </c>
+      <c r="E118" s="22" t="n">
+        <v>281</v>
+      </c>
+      <c r="F118" s="22" t="n">
+        <v>-52</v>
+      </c>
+      <c r="G118" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="H118" s="22" t="n">
+        <v>-42</v>
+      </c>
+      <c r="I118" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="J118" s="22" t="n">
+        <v>-44</v>
+      </c>
+      <c r="K118" s="22" t="n">
+        <v>-122</v>
+      </c>
+      <c r="L118" s="22" t="n">
+        <v>-68</v>
+      </c>
+      <c r="M118" s="22" t="n">
+        <v>227</v>
+      </c>
+      <c r="N118" s="22" t="n">
+        <v>-117</v>
+      </c>
+      <c r="T118" s="22" t="n">
+        <v>137</v>
+      </c>
+      <c r="U118" s="22" t="n">
+        <v>358</v>
+      </c>
+      <c r="V118" s="22" t="n">
+        <v>281</v>
+      </c>
+      <c r="W118" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="X118" s="22" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="20" t="inlineStr">
+        <is>
+          <t>기타포괄손익 합계</t>
+        </is>
+      </c>
+      <c r="C119" s="22" t="n">
+        <v>579</v>
+      </c>
+      <c r="D119" s="22" t="n">
+        <v>1145</v>
+      </c>
+      <c r="E119" s="22" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F119" s="22" t="n">
+        <v>6085</v>
+      </c>
+      <c r="G119" s="22" t="n">
+        <v>-7075</v>
+      </c>
+      <c r="H119" s="22" t="n">
+        <v>368</v>
+      </c>
+      <c r="I119" s="22" t="n">
+        <v>-4392</v>
+      </c>
+      <c r="J119" s="22" t="n">
+        <v>66</v>
+      </c>
+      <c r="K119" s="22" t="n">
+        <v>8591</v>
+      </c>
+      <c r="L119" s="22" t="n">
+        <v>6547</v>
+      </c>
+      <c r="M119" s="22" t="n">
+        <v>-1960</v>
+      </c>
+      <c r="N119" s="22" t="n">
+        <v>64318</v>
+      </c>
+      <c r="T119" s="22" t="n">
+        <v>-3218</v>
+      </c>
+      <c r="U119" s="22" t="n">
+        <v>5255</v>
+      </c>
+      <c r="V119" s="22" t="n">
+        <v>1209</v>
+      </c>
+      <c r="W119" s="22" t="n">
+        <v>-4392</v>
+      </c>
+      <c r="X119" s="22" t="n">
+        <v>-1960</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
+        <is>
+          <t>포괄이익</t>
+        </is>
+      </c>
+      <c r="C120" s="12" t="n">
+        <v>1013</v>
+      </c>
+      <c r="D120" s="12" t="n">
+        <v>2727</v>
+      </c>
+      <c r="E120" s="12" t="n">
+        <v>2924</v>
+      </c>
+      <c r="F120" s="12" t="n">
+        <v>6811</v>
+      </c>
+      <c r="G120" s="12" t="n">
+        <v>-7092</v>
+      </c>
+      <c r="H120" s="12" t="n">
+        <v>1651</v>
+      </c>
+      <c r="I120" s="12" t="n">
+        <v>-2236</v>
+      </c>
+      <c r="J120" s="12" t="n">
+        <v>374</v>
+      </c>
+      <c r="K120" s="12" t="n">
+        <v>9213</v>
+      </c>
+      <c r="L120" s="12" t="n">
+        <v>8459</v>
+      </c>
+      <c r="M120" s="12" t="n">
+        <v>2522</v>
+      </c>
+      <c r="N120" s="12" t="n">
+        <v>65533</v>
+      </c>
+      <c r="T120" s="12" t="n">
+        <v>-2160</v>
+      </c>
+      <c r="U120" s="12" t="n">
+        <v>7219</v>
+      </c>
+      <c r="V120" s="12" t="n">
+        <v>2924</v>
+      </c>
+      <c r="W120" s="12" t="n">
+        <v>-2236</v>
+      </c>
+      <c r="X120" s="12" t="n">
+        <v>2522</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="9" t="inlineStr">
+        <is>
+          <t>지배주주 포괄이익</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="n">
+        <v>1013</v>
+      </c>
+      <c r="D121" s="12" t="n">
+        <v>2727</v>
+      </c>
+      <c r="E121" s="12" t="n">
+        <v>2924</v>
+      </c>
+      <c r="F121" s="12" t="n">
+        <v>6811</v>
+      </c>
+      <c r="G121" s="12" t="n">
+        <v>-7092</v>
+      </c>
+      <c r="H121" s="12" t="n">
+        <v>1651</v>
+      </c>
+      <c r="I121" s="12" t="n">
+        <v>-2236</v>
+      </c>
+      <c r="J121" s="12" t="n">
+        <v>374</v>
+      </c>
+      <c r="K121" s="12" t="n">
+        <v>9213</v>
+      </c>
+      <c r="L121" s="12" t="n">
+        <v>8459</v>
+      </c>
+      <c r="M121" s="12" t="n">
+        <v>2522</v>
+      </c>
+      <c r="N121" s="12" t="n">
+        <v>65533</v>
+      </c>
+      <c r="T121" s="12" t="n">
+        <v>-2160</v>
+      </c>
+      <c r="U121" s="12" t="n">
+        <v>7219</v>
+      </c>
+      <c r="V121" s="12" t="n">
+        <v>2924</v>
+      </c>
+      <c r="W121" s="12" t="n">
+        <v>-2236</v>
+      </c>
+      <c r="X121" s="12" t="n">
+        <v>2522</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="inlineStr">
+        <is>
           <t>비지배주주 포괄이익</t>
         </is>
       </c>
-      <c r="C115" s="12" t="n">
+      <c r="C122" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D115" s="12" t="n">
+      <c r="D122" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E115" s="12" t="n">
+      <c r="E122" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F115" s="12" t="n">
+      <c r="F122" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G115" s="12" t="n">
+      <c r="G122" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H115" s="12" t="n">
+      <c r="H122" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I115" s="12" t="n">
+      <c r="I122" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="J115" s="12" t="n">
+      <c r="J122" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K115" s="12" t="n">
+      <c r="K122" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L115" s="12" t="n">
+      <c r="L122" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="M115" s="12" t="n">
+      <c r="M122" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N115" s="12" t="n">
+      <c r="N122" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="T115" s="12" t="n">
+      <c r="T122" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="U115" s="12" t="n">
+      <c r="U122" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="V115" s="12" t="n">
+      <c r="V122" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="W115" s="12" t="n">
+      <c r="W122" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="X115" s="12" t="n">
+      <c r="X122" s="12" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="18" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="18" t="inlineStr">
         <is>
           <t>현금흐름표 · 전 항목</t>
         </is>
       </c>
-      <c r="B117" s="44" t="inlineStr">
+      <c r="B124" s="44" t="inlineStr">
         <is>
           <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
         </is>
       </c>
-      <c r="C117" s="18" t="n"/>
-      <c r="D117" s="18" t="n"/>
-      <c r="E117" s="18" t="n"/>
-      <c r="F117" s="18" t="n"/>
-      <c r="G117" s="18" t="n"/>
-      <c r="H117" s="18" t="n"/>
-      <c r="I117" s="18" t="n"/>
-      <c r="J117" s="18" t="n"/>
-      <c r="K117" s="18" t="n"/>
-      <c r="L117" s="18" t="n"/>
-      <c r="M117" s="18" t="n"/>
-      <c r="N117" s="18" t="n"/>
-      <c r="O117" s="18" t="n"/>
-      <c r="P117" s="18" t="n"/>
-      <c r="Q117" s="18" t="n"/>
-      <c r="R117" s="18" t="n"/>
-      <c r="S117" s="18" t="n"/>
-      <c r="T117" s="18" t="n"/>
-      <c r="U117" s="18" t="n"/>
-      <c r="V117" s="18" t="n"/>
-      <c r="W117" s="18" t="n"/>
-      <c r="X117" s="18" t="n"/>
-      <c r="Y117" s="18" t="n"/>
-      <c r="Z117" s="18" t="n"/>
-      <c r="AA117" s="18" t="n"/>
-      <c r="AB117" s="18" t="n"/>
-      <c r="AC117" s="18" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="5" t="inlineStr">
+      <c r="C124" s="18" t="n"/>
+      <c r="D124" s="18" t="n"/>
+      <c r="E124" s="18" t="n"/>
+      <c r="F124" s="18" t="n"/>
+      <c r="G124" s="18" t="n"/>
+      <c r="H124" s="18" t="n"/>
+      <c r="I124" s="18" t="n"/>
+      <c r="J124" s="18" t="n"/>
+      <c r="K124" s="18" t="n"/>
+      <c r="L124" s="18" t="n"/>
+      <c r="M124" s="18" t="n"/>
+      <c r="N124" s="18" t="n"/>
+      <c r="O124" s="18" t="n"/>
+      <c r="P124" s="18" t="n"/>
+      <c r="Q124" s="18" t="n"/>
+      <c r="R124" s="18" t="n"/>
+      <c r="S124" s="18" t="n"/>
+      <c r="T124" s="18" t="n"/>
+      <c r="U124" s="18" t="n"/>
+      <c r="V124" s="18" t="n"/>
+      <c r="W124" s="18" t="n"/>
+      <c r="X124" s="18" t="n"/>
+      <c r="Y124" s="18" t="n"/>
+      <c r="Z124" s="18" t="n"/>
+      <c r="AA124" s="18" t="n"/>
+      <c r="AB124" s="18" t="n"/>
+      <c r="AC124" s="18" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B118" s="5" t="inlineStr">
+      <c r="B125" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C118" s="5" t="inlineStr">
+      <c r="C125" s="5" t="inlineStr">
         <is>
           <t>2024.2Q</t>
         </is>
       </c>
-      <c r="D118" s="5" t="inlineStr">
+      <c r="D125" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="E118" s="5" t="inlineStr">
+      <c r="E125" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="F118" s="5" t="inlineStr">
+      <c r="F125" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="G118" s="5" t="inlineStr">
+      <c r="G125" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="H118" s="5" t="inlineStr">
+      <c r="H125" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="I118" s="5" t="inlineStr">
+      <c r="I125" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="J118" s="5" t="inlineStr">
+      <c r="J125" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="K118" s="5" t="inlineStr">
+      <c r="K125" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="L118" s="5" t="inlineStr">
+      <c r="L125" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="M118" s="5" t="inlineStr">
+      <c r="M125" s="5" t="inlineStr">
         <is>
           <t>2026.4Q</t>
         </is>
       </c>
-      <c r="N118" s="5" t="inlineStr">
+      <c r="N125" s="5" t="inlineStr">
         <is>
           <t>2027.1Q</t>
         </is>
       </c>
-      <c r="O118" s="5" t="inlineStr">
+      <c r="O125" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="P118" s="5" t="inlineStr">
+      <c r="P125" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="Q118" s="5" t="inlineStr">
+      <c r="Q125" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="R118" s="5" t="inlineStr">
+      <c r="R125" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="S118" s="5" t="inlineStr">
+      <c r="S125" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="T118" s="5" t="inlineStr">
+      <c r="T125" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U118" s="5" t="inlineStr">
+      <c r="U125" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V118" s="5" t="inlineStr">
+      <c r="V125" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W118" s="5" t="inlineStr">
+      <c r="W125" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="X118" s="5" t="inlineStr">
+      <c r="X125" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y118" s="5" t="inlineStr">
+      <c r="Y125" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="Z118" s="5" t="inlineStr">
+      <c r="Z125" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AA118" s="5" t="inlineStr">
+      <c r="AA125" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AB118" s="5" t="inlineStr">
+      <c r="AB125" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
-      <c r="AC118" s="5" t="inlineStr">
+      <c r="AC125" s="5" t="inlineStr">
         <is>
           <t>2031(MW)</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="9" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="9" t="inlineStr">
         <is>
           <t>법인세차감전 순이익</t>
         </is>
       </c>
-      <c r="C119" s="12" t="n">
+      <c r="C126" s="12" t="n">
         <v>3186</v>
       </c>
-      <c r="E119" s="12" t="n">
+      <c r="E126" s="12" t="n">
         <v>7876</v>
       </c>
-      <c r="G119" s="12" t="n">
+      <c r="G126" s="12" t="n">
         <v>1070</v>
       </c>
-      <c r="I119" s="12" t="n">
+      <c r="I126" s="12" t="n">
         <v>5655</v>
       </c>
-      <c r="K119" s="12" t="n">
+      <c r="K126" s="12" t="n">
         <v>1492</v>
       </c>
-      <c r="M119" s="12" t="n">
+      <c r="M126" s="12" t="n">
         <v>10565</v>
       </c>
-      <c r="O119" s="12" t="n">
+      <c r="O126" s="12" t="n">
         <v>7105</v>
       </c>
-      <c r="P119" s="12" t="n">
+      <c r="P126" s="12" t="n">
         <v>9505</v>
       </c>
-      <c r="Q119" s="12" t="n">
+      <c r="Q126" s="12" t="n">
         <v>5710</v>
       </c>
-      <c r="R119" s="12" t="n">
+      <c r="R126" s="12" t="n">
         <v>6443</v>
       </c>
-      <c r="S119" s="12" t="n">
+      <c r="S126" s="12" t="n">
         <v>8570</v>
       </c>
-      <c r="T119" s="12" t="n">
+      <c r="T126" s="12" t="n">
         <v>11286</v>
       </c>
-      <c r="U119" s="12" t="n">
+      <c r="U126" s="12" t="n">
         <v>8064</v>
       </c>
-      <c r="V119" s="12" t="n">
+      <c r="V126" s="12" t="n">
         <v>7876</v>
       </c>
-      <c r="W119" s="12" t="n">
+      <c r="W126" s="12" t="n">
         <v>5655</v>
       </c>
-      <c r="X119" s="12" t="n">
+      <c r="X126" s="12" t="n">
         <v>10565</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="20" t="inlineStr">
-        <is>
-          <t>감가상각비</t>
-        </is>
-      </c>
-      <c r="C120" s="22" t="n">
-        <v>1280</v>
-      </c>
-      <c r="E120" s="22" t="n">
-        <v>2672</v>
-      </c>
-      <c r="G120" s="22" t="n">
-        <v>1359</v>
-      </c>
-      <c r="I120" s="22" t="n">
-        <v>2936</v>
-      </c>
-      <c r="K120" s="22" t="n">
-        <v>1643</v>
-      </c>
-      <c r="M120" s="22" t="n">
-        <v>3301</v>
-      </c>
-      <c r="O120" s="22" t="n">
-        <v>2093</v>
-      </c>
-      <c r="P120" s="22" t="n">
-        <v>2352</v>
-      </c>
-      <c r="Q120" s="22" t="n">
-        <v>2238</v>
-      </c>
-      <c r="R120" s="22" t="n">
-        <v>2563</v>
-      </c>
-      <c r="S120" s="22" t="n">
-        <v>2655</v>
-      </c>
-      <c r="T120" s="22" t="n">
-        <v>2233</v>
-      </c>
-      <c r="U120" s="22" t="n">
-        <v>2316</v>
-      </c>
-      <c r="V120" s="22" t="n">
-        <v>2672</v>
-      </c>
-      <c r="W120" s="22" t="n">
-        <v>2936</v>
-      </c>
-      <c r="X120" s="22" t="n">
-        <v>3301</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="20" t="inlineStr">
-        <is>
-          <t>영업권 상각</t>
-        </is>
-      </c>
-      <c r="O121" s="22" t="n">
-        <v>273</v>
-      </c>
-      <c r="P121" s="22" t="n">
-        <v>251</v>
-      </c>
-      <c r="Q121" s="22" t="n">
-        <v>513</v>
-      </c>
-      <c r="R121" s="22" t="n">
-        <v>423</v>
-      </c>
-      <c r="S121" s="22" t="n">
-        <v>378</v>
-      </c>
-      <c r="T121" s="22" t="n">
-        <v>378</v>
-      </c>
-      <c r="U121" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="20" t="inlineStr">
-        <is>
-          <t>충당금 증감</t>
-        </is>
-      </c>
-      <c r="C122" s="22" t="n">
-        <v>-325</v>
-      </c>
-      <c r="G122" s="22" t="n">
-        <v>-632</v>
-      </c>
-      <c r="K122" s="22" t="n">
-        <v>-462</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="20" t="inlineStr">
-        <is>
-          <t>퇴직급여부채 증감</t>
-        </is>
-      </c>
-      <c r="C123" s="22" t="n">
-        <v>-125</v>
-      </c>
-      <c r="O123" s="22" t="n">
-        <v>142</v>
-      </c>
-      <c r="P123" s="22" t="n">
-        <v>203</v>
-      </c>
-      <c r="Q123" s="22" t="n">
-        <v>209</v>
-      </c>
-      <c r="R123" s="22" t="n">
-        <v>43</v>
-      </c>
-      <c r="S123" s="22" t="n">
-        <v>126</v>
-      </c>
-      <c r="T123" s="22" t="n">
-        <v>-95</v>
-      </c>
-      <c r="U123" s="22" t="n">
-        <v>-187</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="20" t="inlineStr">
-        <is>
-          <t>투자유가증권 매각손익</t>
-        </is>
-      </c>
-      <c r="C124" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E124" s="22" t="n">
-        <v>-2345</v>
-      </c>
-      <c r="I124" s="22" t="n">
-        <v>-1100</v>
-      </c>
-      <c r="M124" s="22" t="n">
-        <v>-7999</v>
-      </c>
-      <c r="R124" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S124" s="22" t="n">
-        <v>-29</v>
-      </c>
-      <c r="T124" s="22" t="n">
-        <v>-419</v>
-      </c>
-      <c r="U124" s="22" t="n">
-        <v>-1938</v>
-      </c>
-      <c r="V124" s="22" t="n">
-        <v>-2345</v>
-      </c>
-      <c r="W124" s="22" t="n">
-        <v>-1100</v>
-      </c>
-      <c r="X124" s="22" t="n">
-        <v>-7999</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="20" t="inlineStr">
-        <is>
-          <t>손상차손</t>
-        </is>
-      </c>
-      <c r="I125" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" s="22" t="n">
-        <v>497</v>
-      </c>
-      <c r="S125" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T125" s="22" t="n">
-        <v>1243</v>
-      </c>
-      <c r="U125" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W125" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X125" s="22" t="n">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="20" t="inlineStr">
-        <is>
-          <t>투자유가증권 평가손익</t>
-        </is>
-      </c>
-      <c r="Q126" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R126" s="22" t="n">
-        <v>154</v>
-      </c>
-      <c r="S126" s="22" t="n">
-        <v>273</v>
-      </c>
-      <c r="T126" s="22" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각손실</t>
-        </is>
+          <t>감가상각비</t>
+        </is>
+      </c>
+      <c r="C127" s="22" t="n">
+        <v>1280</v>
       </c>
       <c r="E127" s="22" t="n">
-        <v>187</v>
+        <v>2672</v>
+      </c>
+      <c r="G127" s="22" t="n">
+        <v>1359</v>
       </c>
       <c r="I127" s="22" t="n">
-        <v>0</v>
+        <v>2936</v>
+      </c>
+      <c r="K127" s="22" t="n">
+        <v>1643</v>
       </c>
       <c r="M127" s="22" t="n">
-        <v>192</v>
+        <v>3301</v>
+      </c>
+      <c r="O127" s="22" t="n">
+        <v>2093</v>
+      </c>
+      <c r="P127" s="22" t="n">
+        <v>2352</v>
+      </c>
+      <c r="Q127" s="22" t="n">
+        <v>2238</v>
+      </c>
+      <c r="R127" s="22" t="n">
+        <v>2563</v>
+      </c>
+      <c r="S127" s="22" t="n">
+        <v>2655</v>
+      </c>
+      <c r="T127" s="22" t="n">
+        <v>2233</v>
       </c>
       <c r="U127" s="22" t="n">
-        <v>0</v>
+        <v>2316</v>
       </c>
       <c r="V127" s="22" t="n">
-        <v>187</v>
+        <v>2672</v>
       </c>
       <c r="W127" s="22" t="n">
-        <v>0</v>
+        <v>2936</v>
       </c>
       <c r="X127" s="22" t="n">
-        <v>192</v>
+        <v>3301</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="20" t="inlineStr">
         <is>
-          <t>Earthquake Related Expenses Ope CF</t>
-        </is>
-      </c>
-      <c r="E128" s="22" t="n">
-        <v>608</v>
-      </c>
-      <c r="I128" s="22" t="n">
-        <v>0</v>
+          <t>영업권 상각</t>
+        </is>
+      </c>
+      <c r="O128" s="22" t="n">
+        <v>273</v>
+      </c>
+      <c r="P128" s="22" t="n">
+        <v>251</v>
+      </c>
+      <c r="Q128" s="22" t="n">
+        <v>513</v>
+      </c>
+      <c r="R128" s="22" t="n">
+        <v>423</v>
+      </c>
+      <c r="S128" s="22" t="n">
+        <v>378</v>
+      </c>
+      <c r="T128" s="22" t="n">
+        <v>378</v>
       </c>
       <c r="U128" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="V128" s="22" t="n">
-        <v>608</v>
-      </c>
-      <c r="W128" s="22" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="129">
       <c r="A129" s="20" t="inlineStr">
         <is>
-          <t>사업구조개선비용</t>
-        </is>
-      </c>
-      <c r="I129" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M129" s="22" t="n">
-        <v>441</v>
-      </c>
-      <c r="W129" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X129" s="22" t="n">
-        <v>441</v>
+          <t>충당금 증감</t>
+        </is>
+      </c>
+      <c r="C129" s="22" t="n">
+        <v>-325</v>
+      </c>
+      <c r="G129" s="22" t="n">
+        <v>-632</v>
+      </c>
+      <c r="K129" s="22" t="n">
+        <v>-462</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="20" t="inlineStr">
         <is>
-          <t>퇴직급여제도 개정손실</t>
-        </is>
-      </c>
-      <c r="I130" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M130" s="22" t="n">
-        <v>75</v>
-      </c>
-      <c r="W130" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X130" s="22" t="n">
-        <v>75</v>
+          <t>퇴직급여부채 증감</t>
+        </is>
+      </c>
+      <c r="C130" s="22" t="n">
+        <v>-125</v>
+      </c>
+      <c r="O130" s="22" t="n">
+        <v>142</v>
+      </c>
+      <c r="P130" s="22" t="n">
+        <v>203</v>
+      </c>
+      <c r="Q130" s="22" t="n">
+        <v>209</v>
+      </c>
+      <c r="R130" s="22" t="n">
+        <v>43</v>
+      </c>
+      <c r="S130" s="22" t="n">
+        <v>126</v>
+      </c>
+      <c r="T130" s="22" t="n">
+        <v>-95</v>
+      </c>
+      <c r="U130" s="22" t="n">
+        <v>-187</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="20" t="inlineStr">
         <is>
-          <t>상여충당금 증감</t>
-        </is>
+          <t>투자유가증권 매각손익</t>
+        </is>
+      </c>
+      <c r="C131" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="E131" s="22" t="n">
+        <v>-2345</v>
+      </c>
+      <c r="I131" s="22" t="n">
+        <v>-1100</v>
+      </c>
+      <c r="M131" s="22" t="n">
+        <v>-7999</v>
+      </c>
+      <c r="R131" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I131" s="22" t="n">
-        <v>99</v>
-      </c>
-      <c r="M131" s="22" t="n">
-        <v>-44</v>
-      </c>
-      <c r="O131" s="22" t="n">
-        <v>149</v>
-      </c>
-      <c r="P131" s="22" t="n">
-        <v>135</v>
-      </c>
-      <c r="Q131" s="22" t="n">
-        <v>-136</v>
-      </c>
-      <c r="R131" s="22" t="n">
-        <v>135</v>
-      </c>
       <c r="S131" s="22" t="n">
-        <v>151</v>
+        <v>-29</v>
       </c>
       <c r="T131" s="22" t="n">
-        <v>9</v>
+        <v>-419</v>
       </c>
       <c r="U131" s="22" t="n">
-        <v>-11</v>
+        <v>-1938</v>
       </c>
       <c r="V131" s="22" t="n">
-        <v>0</v>
+        <v>-2345</v>
       </c>
       <c r="W131" s="22" t="n">
-        <v>99</v>
+        <v>-1100</v>
       </c>
       <c r="X131" s="22" t="n">
-        <v>-44</v>
+        <v>-7999</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="20" t="inlineStr">
         <is>
-          <t>퇴직급여 자산·부채 증감</t>
-        </is>
-      </c>
-      <c r="C132" s="22" t="n">
-        <v>-125</v>
-      </c>
-      <c r="E132" s="22" t="n">
-        <v>-73</v>
-      </c>
-      <c r="G132" s="22" t="n">
-        <v>-172</v>
+          <t>손상차손</t>
+        </is>
       </c>
       <c r="I132" s="22" t="n">
-        <v>-107</v>
-      </c>
-      <c r="K132" s="22" t="n">
-        <v>-276</v>
+        <v>0</v>
       </c>
       <c r="M132" s="22" t="n">
-        <v>-135</v>
+        <v>497</v>
+      </c>
+      <c r="S132" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T132" s="22" t="n">
+        <v>1243</v>
       </c>
       <c r="U132" s="22" t="n">
-        <v>-187</v>
-      </c>
-      <c r="V132" s="22" t="n">
-        <v>-73</v>
+        <v>0</v>
       </c>
       <c r="W132" s="22" t="n">
-        <v>-107</v>
+        <v>0</v>
       </c>
       <c r="X132" s="22" t="n">
-        <v>-135</v>
+        <v>497</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="20" t="inlineStr">
         <is>
-          <t>대손충당금 증감</t>
-        </is>
-      </c>
-      <c r="E133" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="I133" s="22" t="n">
-        <v>-9</v>
-      </c>
-      <c r="M133" s="22" t="n">
-        <v>-12</v>
-      </c>
-      <c r="O133" s="22" t="n">
-        <v>16</v>
-      </c>
-      <c r="P133" s="22" t="n">
-        <v>-9</v>
+          <t>투자유가증권 평가손익</t>
+        </is>
       </c>
       <c r="Q133" s="22" t="n">
-        <v>-52</v>
+        <v>0</v>
       </c>
       <c r="R133" s="22" t="n">
-        <v>8</v>
+        <v>154</v>
       </c>
       <c r="S133" s="22" t="n">
-        <v>-14</v>
+        <v>273</v>
       </c>
       <c r="T133" s="22" t="n">
-        <v>26</v>
-      </c>
-      <c r="U133" s="22" t="n">
-        <v>-6</v>
-      </c>
-      <c r="V133" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="W133" s="22" t="n">
-        <v>-9</v>
-      </c>
-      <c r="X133" s="22" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="20" t="inlineStr">
         <is>
-          <t>Increase Decrease In Provision For Loss On Order Received Of Software Ope CF</t>
-        </is>
-      </c>
-      <c r="O134" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="P134" s="22" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Q134" s="22" t="n">
+          <t>고정자산 제각손실</t>
+        </is>
+      </c>
+      <c r="E134" s="22" t="n">
+        <v>187</v>
+      </c>
+      <c r="I134" s="22" t="n">
         <v>0</v>
+      </c>
+      <c r="M134" s="22" t="n">
+        <v>192</v>
+      </c>
+      <c r="U134" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V134" s="22" t="n">
+        <v>187</v>
+      </c>
+      <c r="W134" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X134" s="22" t="n">
+        <v>192</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="20" t="inlineStr">
         <is>
-          <t>제품보증 충당금 증감</t>
+          <t>Earthquake Related Expenses Ope CF</t>
         </is>
       </c>
       <c r="E135" s="22" t="n">
-        <v>-166</v>
+        <v>608</v>
       </c>
       <c r="I135" s="22" t="n">
-        <v>-313</v>
-      </c>
-      <c r="M135" s="22" t="n">
-        <v>-276</v>
-      </c>
-      <c r="O135" s="22" t="n">
-        <v>18</v>
-      </c>
-      <c r="P135" s="22" t="n">
-        <v>-36</v>
-      </c>
-      <c r="Q135" s="22" t="n">
-        <v>-168</v>
-      </c>
-      <c r="R135" s="22" t="n">
-        <v>99</v>
-      </c>
-      <c r="S135" s="22" t="n">
-        <v>89</v>
-      </c>
-      <c r="T135" s="22" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="U135" s="22" t="n">
-        <v>-199</v>
+        <v>0</v>
       </c>
       <c r="V135" s="22" t="n">
-        <v>-166</v>
+        <v>608</v>
       </c>
       <c r="W135" s="22" t="n">
-        <v>-313</v>
-      </c>
-      <c r="X135" s="22" t="n">
-        <v>-276</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="20" t="inlineStr">
         <is>
-          <t>Increase Decrease In Provision For Recycling Ope CF</t>
-        </is>
-      </c>
-      <c r="E136" s="22" t="n">
-        <v>-54</v>
+          <t>사업구조개선비용</t>
+        </is>
       </c>
       <c r="I136" s="22" t="n">
-        <v>-78</v>
+        <v>0</v>
       </c>
       <c r="M136" s="22" t="n">
-        <v>-78</v>
-      </c>
-      <c r="O136" s="22" t="n">
-        <v>-95</v>
-      </c>
-      <c r="P136" s="22" t="n">
-        <v>-77</v>
-      </c>
-      <c r="Q136" s="22" t="n">
-        <v>-92</v>
-      </c>
-      <c r="R136" s="22" t="n">
-        <v>-41</v>
-      </c>
-      <c r="S136" s="22" t="n">
-        <v>-17</v>
-      </c>
-      <c r="T136" s="22" t="n">
-        <v>-34</v>
-      </c>
-      <c r="U136" s="22" t="n">
-        <v>-54</v>
-      </c>
-      <c r="V136" s="22" t="n">
-        <v>-54</v>
+        <v>441</v>
       </c>
       <c r="W136" s="22" t="n">
-        <v>-78</v>
+        <v>0</v>
       </c>
       <c r="X136" s="22" t="n">
-        <v>-78</v>
+        <v>441</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수익</t>
-        </is>
-      </c>
-      <c r="E137" s="22" t="n">
-        <v>-1177</v>
+          <t>퇴직급여제도 개정손실</t>
+        </is>
       </c>
       <c r="I137" s="22" t="n">
-        <v>-1298</v>
+        <v>0</v>
       </c>
       <c r="M137" s="22" t="n">
-        <v>-1432</v>
-      </c>
-      <c r="O137" s="22" t="n">
-        <v>-497</v>
-      </c>
-      <c r="P137" s="22" t="n">
-        <v>-547</v>
-      </c>
-      <c r="Q137" s="22" t="n">
-        <v>-638</v>
-      </c>
-      <c r="R137" s="22" t="n">
-        <v>-711</v>
-      </c>
-      <c r="S137" s="22" t="n">
-        <v>-780</v>
-      </c>
-      <c r="T137" s="22" t="n">
-        <v>-933</v>
-      </c>
-      <c r="U137" s="22" t="n">
-        <v>-1098</v>
-      </c>
-      <c r="V137" s="22" t="n">
-        <v>-1177</v>
+        <v>75</v>
       </c>
       <c r="W137" s="22" t="n">
-        <v>-1298</v>
+        <v>0</v>
       </c>
       <c r="X137" s="22" t="n">
-        <v>-1432</v>
+        <v>75</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
-        </is>
-      </c>
-      <c r="C138" s="22" t="n">
-        <v>43</v>
+          <t>상여충당금 증감</t>
+        </is>
       </c>
       <c r="E138" s="22" t="n">
-        <v>90</v>
-      </c>
-      <c r="G138" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" s="22" t="n">
+        <v>99</v>
+      </c>
+      <c r="M138" s="22" t="n">
+        <v>-44</v>
+      </c>
+      <c r="O138" s="22" t="n">
         <v>149</v>
       </c>
-      <c r="I138" s="22" t="n">
-        <v>266</v>
-      </c>
-      <c r="K138" s="22" t="n">
-        <v>87</v>
-      </c>
-      <c r="M138" s="22" t="n">
-        <v>204</v>
-      </c>
-      <c r="O138" s="22" t="n">
-        <v>1</v>
-      </c>
       <c r="P138" s="22" t="n">
-        <v>3</v>
+        <v>135</v>
       </c>
       <c r="Q138" s="22" t="n">
-        <v>2</v>
+        <v>-136</v>
       </c>
       <c r="R138" s="22" t="n">
-        <v>12</v>
+        <v>135</v>
       </c>
       <c r="S138" s="22" t="n">
-        <v>17</v>
+        <v>151</v>
       </c>
       <c r="T138" s="22" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="U138" s="22" t="n">
-        <v>41</v>
+        <v>-11</v>
       </c>
       <c r="V138" s="22" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="W138" s="22" t="n">
-        <v>266</v>
+        <v>99</v>
       </c>
       <c r="X138" s="22" t="n">
-        <v>204</v>
+        <v>-44</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="20" t="inlineStr">
         <is>
-          <t>외환차손익</t>
-        </is>
+          <t>퇴직급여 자산·부채 증감</t>
+        </is>
+      </c>
+      <c r="C139" s="22" t="n">
+        <v>-125</v>
       </c>
       <c r="E139" s="22" t="n">
-        <v>-1020</v>
+        <v>-73</v>
+      </c>
+      <c r="G139" s="22" t="n">
+        <v>-172</v>
       </c>
       <c r="I139" s="22" t="n">
-        <v>-79</v>
+        <v>-107</v>
+      </c>
+      <c r="K139" s="22" t="n">
+        <v>-276</v>
       </c>
       <c r="M139" s="22" t="n">
-        <v>-315</v>
-      </c>
-      <c r="O139" s="22" t="n">
-        <v>128</v>
-      </c>
-      <c r="P139" s="22" t="n">
-        <v>-137</v>
-      </c>
-      <c r="Q139" s="22" t="n">
-        <v>87</v>
-      </c>
-      <c r="R139" s="22" t="n">
-        <v>92</v>
-      </c>
-      <c r="S139" s="22" t="n">
-        <v>-234</v>
-      </c>
-      <c r="T139" s="22" t="n">
-        <v>-156</v>
+        <v>-135</v>
       </c>
       <c r="U139" s="22" t="n">
-        <v>-198</v>
+        <v>-187</v>
       </c>
       <c r="V139" s="22" t="n">
-        <v>-1020</v>
+        <v>-73</v>
       </c>
       <c r="W139" s="22" t="n">
-        <v>-79</v>
+        <v>-107</v>
       </c>
       <c r="X139" s="22" t="n">
-        <v>-315</v>
+        <v>-135</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="20" t="inlineStr">
         <is>
-          <t>유가증권 매각손익</t>
-        </is>
+          <t>대손충당금 증감</t>
+        </is>
+      </c>
+      <c r="E140" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I140" s="22" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M140" s="22" t="n">
+        <v>-12</v>
       </c>
       <c r="O140" s="22" t="n">
-        <v>-11</v>
+        <v>16</v>
       </c>
       <c r="P140" s="22" t="n">
-        <v>0</v>
+        <v>-9</v>
+      </c>
+      <c r="Q140" s="22" t="n">
+        <v>-52</v>
+      </c>
+      <c r="R140" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="S140" s="22" t="n">
+        <v>-14</v>
+      </c>
+      <c r="T140" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="U140" s="22" t="n">
+        <v>-6</v>
+      </c>
+      <c r="V140" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="W140" s="22" t="n">
+        <v>-9</v>
+      </c>
+      <c r="X140" s="22" t="n">
+        <v>-12</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="20" t="inlineStr">
         <is>
-          <t>매출채권 증감</t>
-        </is>
-      </c>
-      <c r="C141" s="22" t="n">
-        <v>4705</v>
-      </c>
-      <c r="E141" s="22" t="n">
-        <v>242</v>
-      </c>
-      <c r="G141" s="22" t="n">
-        <v>3527</v>
-      </c>
-      <c r="I141" s="22" t="n">
-        <v>-88</v>
-      </c>
-      <c r="K141" s="22" t="n">
-        <v>1724</v>
-      </c>
-      <c r="M141" s="22" t="n">
-        <v>-219</v>
+          <t>Increase Decrease In Provision For Loss On Order Received Of Software Ope CF</t>
+        </is>
       </c>
       <c r="O141" s="22" t="n">
-        <v>-98</v>
+        <v>4</v>
       </c>
       <c r="P141" s="22" t="n">
-        <v>-4312</v>
+        <v>-4</v>
       </c>
       <c r="Q141" s="22" t="n">
-        <v>5092</v>
-      </c>
-      <c r="R141" s="22" t="n">
-        <v>-1511</v>
-      </c>
-      <c r="S141" s="22" t="n">
-        <v>-447</v>
-      </c>
-      <c r="T141" s="22" t="n">
-        <v>-4933</v>
-      </c>
-      <c r="U141" s="22" t="n">
-        <v>4566</v>
-      </c>
-      <c r="V141" s="22" t="n">
-        <v>242</v>
-      </c>
-      <c r="W141" s="22" t="n">
-        <v>-88</v>
-      </c>
-      <c r="X141" s="22" t="n">
-        <v>-219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="20" t="inlineStr">
         <is>
-          <t>재고자산 증감</t>
-        </is>
-      </c>
-      <c r="C142" s="22" t="n">
-        <v>-1308</v>
+          <t>제품보증 충당금 증감</t>
+        </is>
       </c>
       <c r="E142" s="22" t="n">
-        <v>7049</v>
-      </c>
-      <c r="G142" s="22" t="n">
-        <v>2646</v>
+        <v>-166</v>
       </c>
       <c r="I142" s="22" t="n">
-        <v>6735</v>
-      </c>
-      <c r="K142" s="22" t="n">
-        <v>-1913</v>
+        <v>-313</v>
       </c>
       <c r="M142" s="22" t="n">
-        <v>1248</v>
+        <v>-276</v>
       </c>
       <c r="O142" s="22" t="n">
-        <v>-731</v>
+        <v>18</v>
       </c>
       <c r="P142" s="22" t="n">
-        <v>541</v>
+        <v>-36</v>
       </c>
       <c r="Q142" s="22" t="n">
-        <v>-4014</v>
+        <v>-168</v>
       </c>
       <c r="R142" s="22" t="n">
-        <v>-1310</v>
+        <v>99</v>
       </c>
       <c r="S142" s="22" t="n">
-        <v>-1158</v>
+        <v>89</v>
       </c>
       <c r="T142" s="22" t="n">
-        <v>341</v>
+        <v>264</v>
       </c>
       <c r="U142" s="22" t="n">
-        <v>-15243</v>
+        <v>-199</v>
       </c>
       <c r="V142" s="22" t="n">
-        <v>7049</v>
+        <v>-166</v>
       </c>
       <c r="W142" s="22" t="n">
-        <v>6735</v>
+        <v>-313</v>
       </c>
       <c r="X142" s="22" t="n">
-        <v>1248</v>
+        <v>-276</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="20" t="inlineStr">
         <is>
-          <t>매입채무 증감</t>
-        </is>
-      </c>
-      <c r="C143" s="22" t="n">
-        <v>-3319</v>
+          <t>Increase Decrease In Provision For Recycling Ope CF</t>
+        </is>
       </c>
       <c r="E143" s="22" t="n">
-        <v>-4207</v>
-      </c>
-      <c r="G143" s="22" t="n">
-        <v>1045</v>
+        <v>-54</v>
       </c>
       <c r="I143" s="22" t="n">
-        <v>1068</v>
-      </c>
-      <c r="K143" s="22" t="n">
-        <v>456</v>
+        <v>-78</v>
       </c>
       <c r="M143" s="22" t="n">
-        <v>-322</v>
+        <v>-78</v>
       </c>
       <c r="O143" s="22" t="n">
-        <v>2025</v>
+        <v>-95</v>
       </c>
       <c r="P143" s="22" t="n">
-        <v>-1067</v>
+        <v>-77</v>
       </c>
       <c r="Q143" s="22" t="n">
-        <v>-682</v>
+        <v>-92</v>
       </c>
       <c r="R143" s="22" t="n">
-        <v>1771</v>
+        <v>-41</v>
       </c>
       <c r="S143" s="22" t="n">
-        <v>-2300</v>
+        <v>-17</v>
       </c>
       <c r="T143" s="22" t="n">
-        <v>946</v>
+        <v>-34</v>
       </c>
       <c r="U143" s="22" t="n">
-        <v>-1052</v>
+        <v>-54</v>
       </c>
       <c r="V143" s="22" t="n">
-        <v>-4207</v>
+        <v>-54</v>
       </c>
       <c r="W143" s="22" t="n">
-        <v>1068</v>
+        <v>-78</v>
       </c>
       <c r="X143" s="22" t="n">
-        <v>-322</v>
+        <v>-78</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C144" s="22" t="n">
-        <v>-1955</v>
+          <t>이자·배당금 수익</t>
+        </is>
       </c>
       <c r="E144" s="22" t="n">
-        <v>237</v>
-      </c>
-      <c r="G144" s="22" t="n">
-        <v>-1968</v>
+        <v>-1177</v>
       </c>
       <c r="I144" s="22" t="n">
-        <v>-832</v>
-      </c>
-      <c r="K144" s="22" t="n">
-        <v>-1300</v>
+        <v>-1298</v>
       </c>
       <c r="M144" s="22" t="n">
-        <v>-35</v>
+        <v>-1432</v>
       </c>
       <c r="O144" s="22" t="n">
-        <v>853</v>
+        <v>-497</v>
       </c>
       <c r="P144" s="22" t="n">
-        <v>-569</v>
+        <v>-547</v>
       </c>
       <c r="Q144" s="22" t="n">
-        <v>-808</v>
+        <v>-638</v>
       </c>
       <c r="R144" s="22" t="n">
-        <v>541</v>
+        <v>-711</v>
       </c>
       <c r="S144" s="22" t="n">
-        <v>348</v>
+        <v>-780</v>
       </c>
       <c r="T144" s="22" t="n">
-        <v>578</v>
+        <v>-933</v>
       </c>
       <c r="U144" s="22" t="n">
-        <v>-56</v>
+        <v>-1098</v>
       </c>
       <c r="V144" s="22" t="n">
-        <v>237</v>
+        <v>-1177</v>
       </c>
       <c r="W144" s="22" t="n">
-        <v>-832</v>
+        <v>-1298</v>
       </c>
       <c r="X144" s="22" t="n">
-        <v>-35</v>
+        <v>-1432</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="20" t="inlineStr">
         <is>
-          <t>소계</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="C145" s="22" t="n">
-        <v>2182</v>
+        <v>43</v>
       </c>
       <c r="E145" s="22" t="n">
-        <v>9921</v>
+        <v>90</v>
       </c>
       <c r="G145" s="22" t="n">
-        <v>7025</v>
+        <v>149</v>
       </c>
       <c r="I145" s="22" t="n">
-        <v>12853</v>
+        <v>266</v>
       </c>
       <c r="K145" s="22" t="n">
-        <v>1450</v>
+        <v>87</v>
       </c>
       <c r="M145" s="22" t="n">
-        <v>5655</v>
+        <v>204</v>
       </c>
       <c r="O145" s="22" t="n">
-        <v>11378</v>
+        <v>1</v>
       </c>
       <c r="P145" s="22" t="n">
-        <v>6231</v>
+        <v>3</v>
       </c>
       <c r="Q145" s="22" t="n">
-        <v>7261</v>
+        <v>2</v>
       </c>
       <c r="R145" s="22" t="n">
-        <v>8712</v>
+        <v>12</v>
       </c>
       <c r="S145" s="22" t="n">
-        <v>7629</v>
+        <v>17</v>
       </c>
       <c r="T145" s="22" t="n">
-        <v>10758</v>
+        <v>21</v>
       </c>
       <c r="U145" s="22" t="n">
-        <v>-5057</v>
+        <v>41</v>
       </c>
       <c r="V145" s="22" t="n">
-        <v>9921</v>
+        <v>90</v>
       </c>
       <c r="W145" s="22" t="n">
-        <v>12853</v>
+        <v>266</v>
       </c>
       <c r="X145" s="22" t="n">
-        <v>5655</v>
+        <v>204</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수취</t>
-        </is>
-      </c>
-      <c r="C146" s="22" t="n">
-        <v>597</v>
+          <t>외환차손익</t>
+        </is>
       </c>
       <c r="E146" s="22" t="n">
-        <v>1182</v>
-      </c>
-      <c r="G146" s="22" t="n">
-        <v>624</v>
+        <v>-1020</v>
       </c>
       <c r="I146" s="22" t="n">
-        <v>1298</v>
-      </c>
-      <c r="K146" s="22" t="n">
-        <v>672</v>
+        <v>-79</v>
       </c>
       <c r="M146" s="22" t="n">
-        <v>1434</v>
+        <v>-315</v>
       </c>
       <c r="O146" s="22" t="n">
-        <v>496</v>
+        <v>128</v>
       </c>
       <c r="P146" s="22" t="n">
-        <v>547</v>
+        <v>-137</v>
       </c>
       <c r="Q146" s="22" t="n">
-        <v>636</v>
+        <v>87</v>
       </c>
       <c r="R146" s="22" t="n">
-        <v>714</v>
+        <v>92</v>
       </c>
       <c r="S146" s="22" t="n">
-        <v>780</v>
+        <v>-234</v>
       </c>
       <c r="T146" s="22" t="n">
-        <v>933</v>
+        <v>-156</v>
       </c>
       <c r="U146" s="22" t="n">
-        <v>1098</v>
+        <v>-198</v>
       </c>
       <c r="V146" s="22" t="n">
-        <v>1182</v>
+        <v>-1020</v>
       </c>
       <c r="W146" s="22" t="n">
-        <v>1298</v>
+        <v>-79</v>
       </c>
       <c r="X146" s="22" t="n">
-        <v>1434</v>
+        <v>-315</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="20" t="inlineStr">
         <is>
-          <t>이자 지급</t>
-        </is>
-      </c>
-      <c r="C147" s="22" t="n">
-        <v>-51</v>
-      </c>
-      <c r="E147" s="22" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G147" s="22" t="n">
-        <v>-147</v>
-      </c>
-      <c r="I147" s="22" t="n">
-        <v>-263</v>
-      </c>
-      <c r="K147" s="22" t="n">
-        <v>-87</v>
-      </c>
-      <c r="M147" s="22" t="n">
-        <v>-206</v>
+          <t>유가증권 매각손익</t>
+        </is>
       </c>
       <c r="O147" s="22" t="n">
-        <v>-1</v>
+        <v>-11</v>
       </c>
       <c r="P147" s="22" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Q147" s="22" t="n">
-        <v>-3</v>
-      </c>
-      <c r="R147" s="22" t="n">
-        <v>-12</v>
-      </c>
-      <c r="S147" s="22" t="n">
-        <v>-17</v>
-      </c>
-      <c r="T147" s="22" t="n">
-        <v>-20</v>
-      </c>
-      <c r="U147" s="22" t="n">
-        <v>-43</v>
-      </c>
-      <c r="V147" s="22" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W147" s="22" t="n">
-        <v>-263</v>
-      </c>
-      <c r="X147" s="22" t="n">
-        <v>-206</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부</t>
+          <t>매출채권 증감</t>
         </is>
       </c>
       <c r="C148" s="22" t="n">
-        <v>-1258</v>
+        <v>4705</v>
       </c>
       <c r="E148" s="22" t="n">
-        <v>-2647</v>
+        <v>242</v>
       </c>
       <c r="G148" s="22" t="n">
-        <v>-1709</v>
+        <v>3527</v>
       </c>
       <c r="I148" s="22" t="n">
-        <v>-2211</v>
+        <v>-88</v>
       </c>
       <c r="K148" s="22" t="n">
-        <v>-853</v>
+        <v>1724</v>
       </c>
       <c r="M148" s="22" t="n">
-        <v>-1312</v>
+        <v>-219</v>
       </c>
       <c r="O148" s="22" t="n">
-        <v>-1340</v>
+        <v>-98</v>
       </c>
       <c r="P148" s="22" t="n">
-        <v>-1946</v>
+        <v>-4312</v>
       </c>
       <c r="Q148" s="22" t="n">
-        <v>-2545</v>
+        <v>5092</v>
       </c>
       <c r="R148" s="22" t="n">
-        <v>-1256</v>
+        <v>-1511</v>
       </c>
       <c r="S148" s="22" t="n">
-        <v>-1792</v>
+        <v>-447</v>
       </c>
       <c r="T148" s="22" t="n">
-        <v>-3241</v>
+        <v>-4933</v>
       </c>
       <c r="U148" s="22" t="n">
-        <v>-3589</v>
+        <v>4566</v>
       </c>
       <c r="V148" s="22" t="n">
-        <v>-2647</v>
+        <v>242</v>
       </c>
       <c r="W148" s="22" t="n">
-        <v>-2211</v>
+        <v>-88</v>
       </c>
       <c r="X148" s="22" t="n">
-        <v>-1312</v>
+        <v>-219</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="20" t="inlineStr">
         <is>
-          <t>사업구조개선 비용 지급액</t>
-        </is>
+          <t>재고자산 증감</t>
+        </is>
+      </c>
+      <c r="C149" s="22" t="n">
+        <v>-1308</v>
+      </c>
+      <c r="E149" s="22" t="n">
+        <v>7049</v>
+      </c>
+      <c r="G149" s="22" t="n">
+        <v>2646</v>
       </c>
       <c r="I149" s="22" t="n">
-        <v>0</v>
+        <v>6735</v>
+      </c>
+      <c r="K149" s="22" t="n">
+        <v>-1913</v>
       </c>
       <c r="M149" s="22" t="n">
-        <v>-4</v>
+        <v>1248</v>
+      </c>
+      <c r="O149" s="22" t="n">
+        <v>-731</v>
+      </c>
+      <c r="P149" s="22" t="n">
+        <v>541</v>
+      </c>
+      <c r="Q149" s="22" t="n">
+        <v>-4014</v>
+      </c>
+      <c r="R149" s="22" t="n">
+        <v>-1310</v>
+      </c>
+      <c r="S149" s="22" t="n">
+        <v>-1158</v>
+      </c>
+      <c r="T149" s="22" t="n">
+        <v>341</v>
+      </c>
+      <c r="U149" s="22" t="n">
+        <v>-15243</v>
+      </c>
+      <c r="V149" s="22" t="n">
+        <v>7049</v>
       </c>
       <c r="W149" s="22" t="n">
-        <v>0</v>
+        <v>6735</v>
       </c>
       <c r="X149" s="22" t="n">
-        <v>-4</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="20" t="inlineStr">
         <is>
-          <t>재해손실 지급</t>
-        </is>
+          <t>매입채무 증감</t>
+        </is>
+      </c>
+      <c r="C150" s="22" t="n">
+        <v>-3319</v>
       </c>
       <c r="E150" s="22" t="n">
-        <v>-442</v>
+        <v>-4207</v>
+      </c>
+      <c r="G150" s="22" t="n">
+        <v>1045</v>
       </c>
       <c r="I150" s="22" t="n">
-        <v>-133</v>
+        <v>1068</v>
+      </c>
+      <c r="K150" s="22" t="n">
+        <v>456</v>
       </c>
       <c r="M150" s="22" t="n">
-        <v>0</v>
+        <v>-322</v>
+      </c>
+      <c r="O150" s="22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="P150" s="22" t="n">
+        <v>-1067</v>
+      </c>
+      <c r="Q150" s="22" t="n">
+        <v>-682</v>
+      </c>
+      <c r="R150" s="22" t="n">
+        <v>1771</v>
+      </c>
+      <c r="S150" s="22" t="n">
+        <v>-2300</v>
+      </c>
+      <c r="T150" s="22" t="n">
+        <v>946</v>
       </c>
       <c r="U150" s="22" t="n">
-        <v>0</v>
+        <v>-1052</v>
       </c>
       <c r="V150" s="22" t="n">
-        <v>-442</v>
+        <v>-4207</v>
       </c>
       <c r="W150" s="22" t="n">
-        <v>-133</v>
+        <v>1068</v>
       </c>
       <c r="X150" s="22" t="n">
-        <v>0</v>
+        <v>-322</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C151" s="12" t="n">
-        <v>1470</v>
-      </c>
-      <c r="E151" s="12" t="n">
-        <v>7914</v>
-      </c>
-      <c r="G151" s="12" t="n">
-        <v>5792</v>
-      </c>
-      <c r="I151" s="12" t="n">
-        <v>11543</v>
-      </c>
-      <c r="K151" s="12" t="n">
-        <v>1180</v>
-      </c>
-      <c r="M151" s="12" t="n">
-        <v>5566</v>
-      </c>
-      <c r="O151" s="12" t="n">
-        <v>10533</v>
-      </c>
-      <c r="P151" s="12" t="n">
-        <v>4829</v>
-      </c>
-      <c r="Q151" s="12" t="n">
-        <v>5348</v>
-      </c>
-      <c r="R151" s="12" t="n">
-        <v>8157</v>
-      </c>
-      <c r="S151" s="12" t="n">
-        <v>6600</v>
-      </c>
-      <c r="T151" s="12" t="n">
-        <v>8429</v>
-      </c>
-      <c r="U151" s="12" t="n">
-        <v>-7592</v>
-      </c>
-      <c r="V151" s="12" t="n">
-        <v>7914</v>
-      </c>
-      <c r="W151" s="12" t="n">
-        <v>11543</v>
-      </c>
-      <c r="X151" s="12" t="n">
-        <v>5566</v>
+      <c r="A151" s="20" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C151" s="22" t="n">
+        <v>-1955</v>
+      </c>
+      <c r="E151" s="22" t="n">
+        <v>237</v>
+      </c>
+      <c r="G151" s="22" t="n">
+        <v>-1968</v>
+      </c>
+      <c r="I151" s="22" t="n">
+        <v>-832</v>
+      </c>
+      <c r="K151" s="22" t="n">
+        <v>-1300</v>
+      </c>
+      <c r="M151" s="22" t="n">
+        <v>-35</v>
+      </c>
+      <c r="O151" s="22" t="n">
+        <v>853</v>
+      </c>
+      <c r="P151" s="22" t="n">
+        <v>-569</v>
+      </c>
+      <c r="Q151" s="22" t="n">
+        <v>-808</v>
+      </c>
+      <c r="R151" s="22" t="n">
+        <v>541</v>
+      </c>
+      <c r="S151" s="22" t="n">
+        <v>348</v>
+      </c>
+      <c r="T151" s="22" t="n">
+        <v>578</v>
+      </c>
+      <c r="U151" s="22" t="n">
+        <v>-56</v>
+      </c>
+      <c r="V151" s="22" t="n">
+        <v>237</v>
+      </c>
+      <c r="W151" s="22" t="n">
+        <v>-832</v>
+      </c>
+      <c r="X151" s="22" t="n">
+        <v>-35</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="20" t="inlineStr">
         <is>
-          <t>정기예금 예입</t>
-        </is>
+          <t>소계</t>
+        </is>
+      </c>
+      <c r="C152" s="22" t="n">
+        <v>2182</v>
+      </c>
+      <c r="E152" s="22" t="n">
+        <v>9921</v>
+      </c>
+      <c r="G152" s="22" t="n">
+        <v>7025</v>
+      </c>
+      <c r="I152" s="22" t="n">
+        <v>12853</v>
+      </c>
+      <c r="K152" s="22" t="n">
+        <v>1450</v>
+      </c>
+      <c r="M152" s="22" t="n">
+        <v>5655</v>
+      </c>
+      <c r="O152" s="22" t="n">
+        <v>11378</v>
       </c>
       <c r="P152" s="22" t="n">
-        <v>0</v>
+        <v>6231</v>
       </c>
       <c r="Q152" s="22" t="n">
-        <v>-300</v>
+        <v>7261</v>
       </c>
       <c r="R152" s="22" t="n">
-        <v>0</v>
+        <v>8712</v>
+      </c>
+      <c r="S152" s="22" t="n">
+        <v>7629</v>
+      </c>
+      <c r="T152" s="22" t="n">
+        <v>10758</v>
+      </c>
+      <c r="U152" s="22" t="n">
+        <v>-5057</v>
+      </c>
+      <c r="V152" s="22" t="n">
+        <v>9921</v>
+      </c>
+      <c r="W152" s="22" t="n">
+        <v>12853</v>
+      </c>
+      <c r="X152" s="22" t="n">
+        <v>5655</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="20" t="inlineStr">
         <is>
-          <t>정기예금 인출</t>
-        </is>
+          <t>이자·배당금 수취</t>
+        </is>
+      </c>
+      <c r="C153" s="22" t="n">
+        <v>597</v>
+      </c>
+      <c r="E153" s="22" t="n">
+        <v>1182</v>
+      </c>
+      <c r="G153" s="22" t="n">
+        <v>624</v>
+      </c>
+      <c r="I153" s="22" t="n">
+        <v>1298</v>
+      </c>
+      <c r="K153" s="22" t="n">
+        <v>672</v>
+      </c>
+      <c r="M153" s="22" t="n">
+        <v>1434</v>
+      </c>
+      <c r="O153" s="22" t="n">
+        <v>496</v>
+      </c>
+      <c r="P153" s="22" t="n">
+        <v>547</v>
       </c>
       <c r="Q153" s="22" t="n">
-        <v>0</v>
+        <v>636</v>
       </c>
       <c r="R153" s="22" t="n">
-        <v>300</v>
+        <v>714</v>
       </c>
       <c r="S153" s="22" t="n">
-        <v>0</v>
+        <v>780</v>
+      </c>
+      <c r="T153" s="22" t="n">
+        <v>933</v>
+      </c>
+      <c r="U153" s="22" t="n">
+        <v>1098</v>
+      </c>
+      <c r="V153" s="22" t="n">
+        <v>1182</v>
+      </c>
+      <c r="W153" s="22" t="n">
+        <v>1298</v>
+      </c>
+      <c r="X153" s="22" t="n">
+        <v>1434</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="20" t="inlineStr">
         <is>
-          <t>유가증권 취득</t>
-        </is>
+          <t>이자 지급</t>
+        </is>
+      </c>
+      <c r="C154" s="22" t="n">
+        <v>-51</v>
+      </c>
+      <c r="E154" s="22" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G154" s="22" t="n">
+        <v>-147</v>
+      </c>
+      <c r="I154" s="22" t="n">
+        <v>-263</v>
+      </c>
+      <c r="K154" s="22" t="n">
+        <v>-87</v>
+      </c>
+      <c r="M154" s="22" t="n">
+        <v>-206</v>
       </c>
       <c r="O154" s="22" t="n">
-        <v>-28</v>
+        <v>-1</v>
       </c>
       <c r="P154" s="22" t="n">
-        <v>-300</v>
+        <v>-2</v>
       </c>
       <c r="Q154" s="22" t="n">
-        <v>-500</v>
+        <v>-3</v>
       </c>
       <c r="R154" s="22" t="n">
-        <v>0</v>
+        <v>-12</v>
+      </c>
+      <c r="S154" s="22" t="n">
+        <v>-17</v>
+      </c>
+      <c r="T154" s="22" t="n">
+        <v>-20</v>
+      </c>
+      <c r="U154" s="22" t="n">
+        <v>-43</v>
+      </c>
+      <c r="V154" s="22" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W154" s="22" t="n">
+        <v>-263</v>
+      </c>
+      <c r="X154" s="22" t="n">
+        <v>-206</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="20" t="inlineStr">
         <is>
-          <t>유가증권 매각·상환 수입</t>
-        </is>
+          <t>법인세 납부</t>
+        </is>
+      </c>
+      <c r="C155" s="22" t="n">
+        <v>-1258</v>
       </c>
       <c r="E155" s="22" t="n">
-        <v>0</v>
+        <v>-2647</v>
+      </c>
+      <c r="G155" s="22" t="n">
+        <v>-1709</v>
+      </c>
+      <c r="I155" s="22" t="n">
+        <v>-2211</v>
+      </c>
+      <c r="K155" s="22" t="n">
+        <v>-853</v>
+      </c>
+      <c r="M155" s="22" t="n">
+        <v>-1312</v>
       </c>
       <c r="O155" s="22" t="n">
-        <v>509</v>
+        <v>-1340</v>
       </c>
       <c r="P155" s="22" t="n">
-        <v>1</v>
+        <v>-1946</v>
       </c>
       <c r="Q155" s="22" t="n">
-        <v>302</v>
+        <v>-2545</v>
       </c>
       <c r="R155" s="22" t="n">
-        <v>321</v>
+        <v>-1256</v>
       </c>
       <c r="S155" s="22" t="n">
-        <v>805</v>
+        <v>-1792</v>
       </c>
       <c r="T155" s="22" t="n">
-        <v>1000</v>
+        <v>-3241</v>
       </c>
       <c r="U155" s="22" t="n">
-        <v>300</v>
+        <v>-3589</v>
       </c>
       <c r="V155" s="22" t="n">
-        <v>0</v>
+        <v>-2647</v>
+      </c>
+      <c r="W155" s="22" t="n">
+        <v>-2211</v>
+      </c>
+      <c r="X155" s="22" t="n">
+        <v>-1312</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="20" t="inlineStr">
         <is>
-          <t>Purchase Of Property Plant And Equipment And Intangible Assets Inv CF</t>
-        </is>
-      </c>
-      <c r="C156" s="22" t="n">
-        <v>-2129</v>
-      </c>
-      <c r="G156" s="22" t="n">
-        <v>-1016</v>
-      </c>
-      <c r="K156" s="22" t="n">
-        <v>-4020</v>
+          <t>사업구조개선 비용 지급액</t>
+        </is>
+      </c>
+      <c r="I156" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" s="22" t="n">
+        <v>-4</v>
+      </c>
+      <c r="W156" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X156" s="22" t="n">
+        <v>-4</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="20" t="inlineStr">
         <is>
-          <t>Purchase Of Short Term And Long Term Investment Securities Inv CF</t>
-        </is>
-      </c>
-      <c r="C157" s="22" t="n">
-        <v>-301</v>
-      </c>
-      <c r="G157" s="22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K157" s="22" t="n">
-        <v>-101</v>
+          <t>재해손실 지급</t>
+        </is>
+      </c>
+      <c r="E157" s="22" t="n">
+        <v>-442</v>
+      </c>
+      <c r="I157" s="22" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M157" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U157" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V157" s="22" t="n">
+        <v>-442</v>
+      </c>
+      <c r="W157" s="22" t="n">
+        <v>-133</v>
+      </c>
+      <c r="X157" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="20" t="inlineStr">
-        <is>
-          <t>유가증권·투자유가증권 매각·상환 수입</t>
-        </is>
-      </c>
-      <c r="C158" s="22" t="n">
-        <v>49</v>
-      </c>
-      <c r="G158" s="22" t="n">
-        <v>29</v>
-      </c>
-      <c r="K158" s="22" t="n">
-        <v>0</v>
+      <c r="A158" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C158" s="12" t="n">
+        <v>1470</v>
+      </c>
+      <c r="E158" s="12" t="n">
+        <v>7914</v>
+      </c>
+      <c r="G158" s="12" t="n">
+        <v>5792</v>
+      </c>
+      <c r="I158" s="12" t="n">
+        <v>11543</v>
+      </c>
+      <c r="K158" s="12" t="n">
+        <v>1180</v>
+      </c>
+      <c r="M158" s="12" t="n">
+        <v>5566</v>
+      </c>
+      <c r="O158" s="12" t="n">
+        <v>10533</v>
+      </c>
+      <c r="P158" s="12" t="n">
+        <v>4829</v>
+      </c>
+      <c r="Q158" s="12" t="n">
+        <v>5348</v>
+      </c>
+      <c r="R158" s="12" t="n">
+        <v>8157</v>
+      </c>
+      <c r="S158" s="12" t="n">
+        <v>6600</v>
+      </c>
+      <c r="T158" s="12" t="n">
+        <v>8429</v>
+      </c>
+      <c r="U158" s="12" t="n">
+        <v>-7592</v>
+      </c>
+      <c r="V158" s="12" t="n">
+        <v>7914</v>
+      </c>
+      <c r="W158" s="12" t="n">
+        <v>11543</v>
+      </c>
+      <c r="X158" s="12" t="n">
+        <v>5566</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="20" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
-        </is>
-      </c>
-      <c r="E159" s="22" t="n">
-        <v>-2931</v>
-      </c>
-      <c r="I159" s="22" t="n">
-        <v>-3549</v>
-      </c>
-      <c r="M159" s="22" t="n">
-        <v>-4627</v>
-      </c>
-      <c r="O159" s="22" t="n">
-        <v>-3027</v>
+          <t>정기예금 예입</t>
+        </is>
       </c>
       <c r="P159" s="22" t="n">
-        <v>-2787</v>
+        <v>0</v>
       </c>
       <c r="Q159" s="22" t="n">
-        <v>-3840</v>
+        <v>-300</v>
       </c>
       <c r="R159" s="22" t="n">
-        <v>-4041</v>
-      </c>
-      <c r="S159" s="22" t="n">
-        <v>-3103</v>
-      </c>
-      <c r="T159" s="22" t="n">
-        <v>-2768</v>
-      </c>
-      <c r="U159" s="22" t="n">
-        <v>-1962</v>
-      </c>
-      <c r="V159" s="22" t="n">
-        <v>-2931</v>
-      </c>
-      <c r="W159" s="22" t="n">
-        <v>-3549</v>
-      </c>
-      <c r="X159" s="22" t="n">
-        <v>-4627</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="20" t="inlineStr">
         <is>
-          <t>Increase In Other Assets Inv CF</t>
-        </is>
-      </c>
-      <c r="E160" s="22" t="n">
-        <v>-393</v>
-      </c>
-      <c r="I160" s="22" t="n">
-        <v>-494</v>
-      </c>
-      <c r="M160" s="22" t="n">
-        <v>-266</v>
-      </c>
-      <c r="O160" s="22" t="n">
-        <v>-367</v>
-      </c>
-      <c r="P160" s="22" t="n">
-        <v>-156</v>
+          <t>정기예금 인출</t>
+        </is>
       </c>
       <c r="Q160" s="22" t="n">
-        <v>-192</v>
+        <v>0</v>
       </c>
       <c r="R160" s="22" t="n">
-        <v>-243</v>
+        <v>300</v>
       </c>
       <c r="S160" s="22" t="n">
-        <v>-411</v>
-      </c>
-      <c r="T160" s="22" t="n">
-        <v>-503</v>
-      </c>
-      <c r="U160" s="22" t="n">
-        <v>-183</v>
-      </c>
-      <c r="V160" s="22" t="n">
-        <v>-393</v>
-      </c>
-      <c r="W160" s="22" t="n">
-        <v>-494</v>
-      </c>
-      <c r="X160" s="22" t="n">
-        <v>-266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 취득</t>
-        </is>
-      </c>
-      <c r="E161" s="22" t="n">
-        <v>-302</v>
-      </c>
-      <c r="I161" s="22" t="n">
-        <v>-3</v>
-      </c>
-      <c r="M161" s="22" t="n">
-        <v>-104</v>
+          <t>유가증권 취득</t>
+        </is>
       </c>
       <c r="O161" s="22" t="n">
-        <v>-5</v>
+        <v>-28</v>
       </c>
       <c r="P161" s="22" t="n">
-        <v>-778</v>
+        <v>-300</v>
       </c>
       <c r="Q161" s="22" t="n">
-        <v>-4155</v>
+        <v>-500</v>
       </c>
       <c r="R161" s="22" t="n">
-        <v>-521</v>
-      </c>
-      <c r="S161" s="22" t="n">
-        <v>-780</v>
-      </c>
-      <c r="T161" s="22" t="n">
-        <v>-901</v>
-      </c>
-      <c r="U161" s="22" t="n">
-        <v>-2</v>
-      </c>
-      <c r="V161" s="22" t="n">
-        <v>-302</v>
-      </c>
-      <c r="W161" s="22" t="n">
-        <v>-3</v>
-      </c>
-      <c r="X161" s="22" t="n">
-        <v>-104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각·상환 수입</t>
+          <t>유가증권 매각·상환 수입</t>
         </is>
       </c>
       <c r="E162" s="22" t="n">
-        <v>2735</v>
-      </c>
-      <c r="I162" s="22" t="n">
-        <v>1858</v>
-      </c>
-      <c r="M162" s="22" t="n">
-        <v>6724</v>
+        <v>0</v>
       </c>
       <c r="O162" s="22" t="n">
-        <v>2</v>
+        <v>509</v>
       </c>
       <c r="P162" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q162" s="22" t="n">
+        <v>302</v>
+      </c>
+      <c r="R162" s="22" t="n">
+        <v>321</v>
+      </c>
+      <c r="S162" s="22" t="n">
+        <v>805</v>
+      </c>
+      <c r="T162" s="22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U162" s="22" t="n">
+        <v>300</v>
+      </c>
+      <c r="V162" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="R162" s="22" t="n">
-        <v>458</v>
-      </c>
-      <c r="S162" s="22" t="n">
-        <v>76</v>
-      </c>
-      <c r="T162" s="22" t="n">
-        <v>666</v>
-      </c>
-      <c r="U162" s="22" t="n">
-        <v>2653</v>
-      </c>
-      <c r="V162" s="22" t="n">
-        <v>2735</v>
-      </c>
-      <c r="W162" s="22" t="n">
-        <v>1858</v>
-      </c>
-      <c r="X162" s="22" t="n">
-        <v>6724</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="20" t="inlineStr">
         <is>
-          <t>대여</t>
-        </is>
-      </c>
-      <c r="O163" s="22" t="n">
-        <v>-108</v>
-      </c>
-      <c r="P163" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q163" s="22" t="n">
-        <v>-51</v>
-      </c>
-      <c r="R163" s="22" t="n">
-        <v>-13</v>
-      </c>
-      <c r="S163" s="22" t="n">
-        <v>-13</v>
-      </c>
-      <c r="T163" s="22" t="n">
-        <v>0</v>
+          <t>Purchase Of Property Plant And Equipment And Intangible Assets Inv CF</t>
+        </is>
+      </c>
+      <c r="C163" s="22" t="n">
+        <v>-2129</v>
+      </c>
+      <c r="G163" s="22" t="n">
+        <v>-1016</v>
+      </c>
+      <c r="K163" s="22" t="n">
+        <v>-4020</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="20" t="inlineStr">
         <is>
-          <t>대여금 회수</t>
-        </is>
-      </c>
-      <c r="E164" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I164" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="M164" s="22" t="n">
-        <v>25</v>
-      </c>
-      <c r="O164" s="22" t="n">
-        <v>24</v>
-      </c>
-      <c r="P164" s="22" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q164" s="22" t="n">
-        <v>17</v>
-      </c>
-      <c r="R164" s="22" t="n">
-        <v>72</v>
-      </c>
-      <c r="S164" s="22" t="n">
-        <v>31</v>
-      </c>
-      <c r="T164" s="22" t="n">
-        <v>36</v>
-      </c>
-      <c r="U164" s="22" t="n">
-        <v>20</v>
-      </c>
-      <c r="V164" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W164" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="X164" s="22" t="n">
-        <v>25</v>
+          <t>유가증권 및 투자유가증권 취득 지출</t>
+        </is>
+      </c>
+      <c r="C164" s="22" t="n">
+        <v>-301</v>
+      </c>
+      <c r="G164" s="22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K164" s="22" t="n">
+        <v>-101</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="20" t="inlineStr">
         <is>
-          <t>사업양수 지출</t>
-        </is>
-      </c>
-      <c r="O165" s="22" t="n">
-        <v>-1251</v>
-      </c>
-      <c r="P165" s="22" t="n">
+          <t>유가증권·투자유가증권 매각·상환 수입</t>
+        </is>
+      </c>
+      <c r="C165" s="22" t="n">
+        <v>49</v>
+      </c>
+      <c r="G165" s="22" t="n">
+        <v>29</v>
+      </c>
+      <c r="K165" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="20" t="inlineStr">
         <is>
-          <t>연결범위 변경 자회사 주식 취득</t>
-        </is>
+          <t>유형자산 취득(설비투자)</t>
+        </is>
+      </c>
+      <c r="E166" s="22" t="n">
+        <v>-2931</v>
+      </c>
+      <c r="I166" s="22" t="n">
+        <v>-3549</v>
+      </c>
+      <c r="M166" s="22" t="n">
+        <v>-4627</v>
       </c>
       <c r="O166" s="22" t="n">
-        <v>0</v>
+        <v>-3027</v>
       </c>
       <c r="P166" s="22" t="n">
-        <v>-2566</v>
+        <v>-2787</v>
       </c>
       <c r="Q166" s="22" t="n">
-        <v>0</v>
+        <v>-3840</v>
+      </c>
+      <c r="R166" s="22" t="n">
+        <v>-4041</v>
+      </c>
+      <c r="S166" s="22" t="n">
+        <v>-3103</v>
+      </c>
+      <c r="T166" s="22" t="n">
+        <v>-2768</v>
+      </c>
+      <c r="U166" s="22" t="n">
+        <v>-1962</v>
+      </c>
+      <c r="V166" s="22" t="n">
+        <v>-2931</v>
+      </c>
+      <c r="W166" s="22" t="n">
+        <v>-3549</v>
+      </c>
+      <c r="X166" s="22" t="n">
+        <v>-4627</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C167" s="22" t="n">
-        <v>-22</v>
+          <t>Increase In Other Assets Inv CF</t>
+        </is>
       </c>
       <c r="E167" s="22" t="n">
-        <v>-165</v>
-      </c>
-      <c r="G167" s="22" t="n">
-        <v>-16</v>
+        <v>-393</v>
       </c>
       <c r="I167" s="22" t="n">
-        <v>36</v>
-      </c>
-      <c r="K167" s="22" t="n">
-        <v>19</v>
+        <v>-494</v>
       </c>
       <c r="M167" s="22" t="n">
-        <v>-63</v>
+        <v>-266</v>
       </c>
       <c r="O167" s="22" t="n">
-        <v>95</v>
+        <v>-367</v>
       </c>
       <c r="P167" s="22" t="n">
-        <v>-1</v>
+        <v>-156</v>
       </c>
       <c r="Q167" s="22" t="n">
-        <v>7</v>
+        <v>-192</v>
       </c>
       <c r="R167" s="22" t="n">
-        <v>-49</v>
+        <v>-243</v>
       </c>
       <c r="S167" s="22" t="n">
-        <v>61</v>
+        <v>-411</v>
       </c>
       <c r="T167" s="22" t="n">
-        <v>76</v>
+        <v>-503</v>
       </c>
       <c r="U167" s="22" t="n">
-        <v>26</v>
+        <v>-183</v>
       </c>
       <c r="V167" s="22" t="n">
-        <v>-165</v>
+        <v>-393</v>
       </c>
       <c r="W167" s="22" t="n">
-        <v>36</v>
+        <v>-494</v>
       </c>
       <c r="X167" s="22" t="n">
-        <v>-63</v>
+        <v>-266</v>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C168" s="12" t="n">
-        <v>-2403</v>
-      </c>
-      <c r="E168" s="12" t="n">
-        <v>-1057</v>
-      </c>
-      <c r="G168" s="12" t="n">
-        <v>-1005</v>
-      </c>
-      <c r="I168" s="12" t="n">
-        <v>-2140</v>
-      </c>
-      <c r="K168" s="12" t="n">
-        <v>-4103</v>
-      </c>
-      <c r="M168" s="12" t="n">
-        <v>1687</v>
-      </c>
-      <c r="O168" s="12" t="n">
-        <v>-4157</v>
-      </c>
-      <c r="P168" s="12" t="n">
-        <v>-6567</v>
-      </c>
-      <c r="Q168" s="12" t="n">
-        <v>-8713</v>
-      </c>
-      <c r="R168" s="12" t="n">
-        <v>-3717</v>
-      </c>
-      <c r="S168" s="12" t="n">
-        <v>-3333</v>
-      </c>
-      <c r="T168" s="12" t="n">
-        <v>-2394</v>
-      </c>
-      <c r="U168" s="12" t="n">
-        <v>853</v>
-      </c>
-      <c r="V168" s="12" t="n">
-        <v>-1057</v>
-      </c>
-      <c r="W168" s="12" t="n">
-        <v>-2140</v>
-      </c>
-      <c r="X168" s="12" t="n">
-        <v>1687</v>
+      <c r="A168" s="20" t="inlineStr">
+        <is>
+          <t>투자유가증권 취득</t>
+        </is>
+      </c>
+      <c r="E168" s="22" t="n">
+        <v>-302</v>
+      </c>
+      <c r="I168" s="22" t="n">
+        <v>-3</v>
+      </c>
+      <c r="M168" s="22" t="n">
+        <v>-104</v>
+      </c>
+      <c r="O168" s="22" t="n">
+        <v>-5</v>
+      </c>
+      <c r="P168" s="22" t="n">
+        <v>-778</v>
+      </c>
+      <c r="Q168" s="22" t="n">
+        <v>-4155</v>
+      </c>
+      <c r="R168" s="22" t="n">
+        <v>-521</v>
+      </c>
+      <c r="S168" s="22" t="n">
+        <v>-780</v>
+      </c>
+      <c r="T168" s="22" t="n">
+        <v>-901</v>
+      </c>
+      <c r="U168" s="22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V168" s="22" t="n">
+        <v>-302</v>
+      </c>
+      <c r="W168" s="22" t="n">
+        <v>-3</v>
+      </c>
+      <c r="X168" s="22" t="n">
+        <v>-104</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="20" t="inlineStr">
         <is>
-          <t>단기차입</t>
-        </is>
-      </c>
-      <c r="C169" s="22" t="n">
-        <v>6500</v>
-      </c>
-      <c r="G169" s="22" t="n">
+          <t>투자유가증권 매각·상환 수입</t>
+        </is>
+      </c>
+      <c r="E169" s="22" t="n">
+        <v>2735</v>
+      </c>
+      <c r="I169" s="22" t="n">
+        <v>1858</v>
+      </c>
+      <c r="M169" s="22" t="n">
+        <v>6724</v>
+      </c>
+      <c r="O169" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P169" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q169" s="22" t="n">
         <v>0</v>
+      </c>
+      <c r="R169" s="22" t="n">
+        <v>458</v>
+      </c>
+      <c r="S169" s="22" t="n">
+        <v>76</v>
+      </c>
+      <c r="T169" s="22" t="n">
+        <v>666</v>
+      </c>
+      <c r="U169" s="22" t="n">
+        <v>2653</v>
+      </c>
+      <c r="V169" s="22" t="n">
+        <v>2735</v>
+      </c>
+      <c r="W169" s="22" t="n">
+        <v>1858</v>
+      </c>
+      <c r="X169" s="22" t="n">
+        <v>6724</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="20" t="inlineStr">
         <is>
-          <t>단기차입금 순증감</t>
-        </is>
-      </c>
-      <c r="E170" s="22" t="n">
-        <v>3333</v>
-      </c>
-      <c r="I170" s="22" t="n">
+          <t>대여</t>
+        </is>
+      </c>
+      <c r="O170" s="22" t="n">
+        <v>-108</v>
+      </c>
+      <c r="P170" s="22" t="n">
         <v>0</v>
+      </c>
+      <c r="Q170" s="22" t="n">
+        <v>-51</v>
+      </c>
+      <c r="R170" s="22" t="n">
+        <v>-13</v>
+      </c>
+      <c r="S170" s="22" t="n">
+        <v>-13</v>
       </c>
       <c r="T170" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="U170" s="22" t="n">
-        <v>-629</v>
-      </c>
-      <c r="V170" s="22" t="n">
-        <v>3333</v>
-      </c>
-      <c r="W170" s="22" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="171">
       <c r="A171" s="20" t="inlineStr">
         <is>
-          <t>장기차입금 상환</t>
-        </is>
-      </c>
-      <c r="C171" s="22" t="n">
-        <v>-76</v>
+          <t>대여금 회수</t>
+        </is>
       </c>
       <c r="E171" s="22" t="n">
-        <v>-156</v>
-      </c>
-      <c r="G171" s="22" t="n">
-        <v>-83</v>
+        <v>0</v>
       </c>
       <c r="I171" s="22" t="n">
-        <v>-163</v>
-      </c>
-      <c r="K171" s="22" t="n">
-        <v>-84</v>
+        <v>12</v>
       </c>
       <c r="M171" s="22" t="n">
-        <v>-174</v>
+        <v>25</v>
       </c>
       <c r="O171" s="22" t="n">
+        <v>24</v>
+      </c>
+      <c r="P171" s="22" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q171" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="R171" s="22" t="n">
+        <v>72</v>
+      </c>
+      <c r="S171" s="22" t="n">
+        <v>31</v>
+      </c>
+      <c r="T171" s="22" t="n">
+        <v>36</v>
+      </c>
+      <c r="U171" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="V171" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="P171" s="22" t="n">
-        <v>-959</v>
-      </c>
-      <c r="Q171" s="22" t="n">
-        <v>-55</v>
-      </c>
-      <c r="R171" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S171" s="22" t="n">
-        <v>-61</v>
-      </c>
-      <c r="T171" s="22" t="n">
-        <v>-130</v>
-      </c>
-      <c r="U171" s="22" t="n">
-        <v>-140</v>
-      </c>
-      <c r="V171" s="22" t="n">
-        <v>-156</v>
-      </c>
       <c r="W171" s="22" t="n">
-        <v>-163</v>
+        <v>12</v>
       </c>
       <c r="X171" s="22" t="n">
-        <v>-174</v>
+        <v>25</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="20" t="inlineStr">
         <is>
-          <t>장기차입</t>
-        </is>
+          <t>사업양수 지출</t>
+        </is>
+      </c>
+      <c r="O172" s="22" t="n">
+        <v>-1251</v>
       </c>
       <c r="P172" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="Q172" s="22" t="n">
-        <v>1284</v>
-      </c>
-      <c r="R172" s="22" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="173">
       <c r="A173" s="20" t="inlineStr">
         <is>
-          <t>리스부채 상환</t>
-        </is>
-      </c>
-      <c r="C173" s="22" t="n">
-        <v>-158</v>
-      </c>
-      <c r="E173" s="22" t="n">
-        <v>-315</v>
-      </c>
-      <c r="G173" s="22" t="n">
-        <v>-151</v>
-      </c>
-      <c r="I173" s="22" t="n">
-        <v>-329</v>
-      </c>
-      <c r="K173" s="22" t="n">
-        <v>-197</v>
-      </c>
-      <c r="M173" s="22" t="n">
-        <v>-402</v>
+          <t>연결범위 변경 자회사 주식 취득</t>
+        </is>
+      </c>
+      <c r="O173" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P173" s="22" t="n">
+        <v>-2566</v>
       </c>
       <c r="Q173" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="R173" s="22" t="n">
-        <v>-194</v>
-      </c>
-      <c r="S173" s="22" t="n">
-        <v>-240</v>
-      </c>
-      <c r="T173" s="22" t="n">
-        <v>-209</v>
-      </c>
-      <c r="U173" s="22" t="n">
-        <v>-234</v>
-      </c>
-      <c r="V173" s="22" t="n">
-        <v>-315</v>
-      </c>
-      <c r="W173" s="22" t="n">
-        <v>-329</v>
-      </c>
-      <c r="X173" s="22" t="n">
-        <v>-402</v>
-      </c>
     </row>
     <row r="174">
       <c r="A174" s="20" t="inlineStr">
         <is>
-          <t>자기주식 취득</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C174" s="22" t="n">
+        <v>-22</v>
+      </c>
+      <c r="E174" s="22" t="n">
+        <v>-165</v>
+      </c>
+      <c r="G174" s="22" t="n">
+        <v>-16</v>
+      </c>
+      <c r="I174" s="22" t="n">
+        <v>36</v>
+      </c>
+      <c r="K174" s="22" t="n">
+        <v>19</v>
+      </c>
+      <c r="M174" s="22" t="n">
+        <v>-63</v>
+      </c>
+      <c r="O174" s="22" t="n">
+        <v>95</v>
+      </c>
+      <c r="P174" s="22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q174" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="R174" s="22" t="n">
+        <v>-49</v>
+      </c>
+      <c r="S174" s="22" t="n">
+        <v>61</v>
+      </c>
+      <c r="T174" s="22" t="n">
+        <v>76</v>
+      </c>
+      <c r="U174" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="V174" s="22" t="n">
+        <v>-165</v>
+      </c>
+      <c r="W174" s="22" t="n">
+        <v>36</v>
+      </c>
+      <c r="X174" s="22" t="n">
+        <v>-63</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C175" s="12" t="n">
+        <v>-2403</v>
+      </c>
+      <c r="E175" s="12" t="n">
+        <v>-1057</v>
+      </c>
+      <c r="G175" s="12" t="n">
+        <v>-1005</v>
+      </c>
+      <c r="I175" s="12" t="n">
+        <v>-2140</v>
+      </c>
+      <c r="K175" s="12" t="n">
+        <v>-4103</v>
+      </c>
+      <c r="M175" s="12" t="n">
+        <v>1687</v>
+      </c>
+      <c r="O175" s="12" t="n">
+        <v>-4157</v>
+      </c>
+      <c r="P175" s="12" t="n">
+        <v>-6567</v>
+      </c>
+      <c r="Q175" s="12" t="n">
+        <v>-8713</v>
+      </c>
+      <c r="R175" s="12" t="n">
+        <v>-3717</v>
+      </c>
+      <c r="S175" s="12" t="n">
+        <v>-3333</v>
+      </c>
+      <c r="T175" s="12" t="n">
+        <v>-2394</v>
+      </c>
+      <c r="U175" s="12" t="n">
+        <v>853</v>
+      </c>
+      <c r="V175" s="12" t="n">
+        <v>-1057</v>
+      </c>
+      <c r="W175" s="12" t="n">
+        <v>-2140</v>
+      </c>
+      <c r="X175" s="12" t="n">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="20" t="inlineStr">
+        <is>
+          <t>단기차입</t>
+        </is>
+      </c>
+      <c r="C176" s="22" t="n">
+        <v>6500</v>
+      </c>
+      <c r="G176" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="E174" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I174" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M174" s="22" t="n">
-        <v>-3582</v>
-      </c>
-      <c r="O174" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="P174" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q174" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="R174" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="S174" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="T174" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="U174" s="22" t="n">
-        <v>-2821</v>
-      </c>
-      <c r="V174" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="W174" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X174" s="22" t="n">
-        <v>-3582</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="20" t="inlineStr">
-        <is>
-          <t>배당금 지급</t>
-        </is>
-      </c>
-      <c r="C175" s="22" t="n">
-        <v>-1337</v>
-      </c>
-      <c r="E175" s="22" t="n">
-        <v>-3393</v>
-      </c>
-      <c r="G175" s="22" t="n">
-        <v>-2056</v>
-      </c>
-      <c r="I175" s="22" t="n">
-        <v>-4218</v>
-      </c>
-      <c r="K175" s="22" t="n">
-        <v>-2160</v>
-      </c>
-      <c r="M175" s="22" t="n">
-        <v>-4425</v>
-      </c>
-      <c r="O175" s="22" t="n">
-        <v>-1598</v>
-      </c>
-      <c r="P175" s="22" t="n">
-        <v>-1812</v>
-      </c>
-      <c r="Q175" s="22" t="n">
-        <v>-2025</v>
-      </c>
-      <c r="R175" s="22" t="n">
-        <v>-2238</v>
-      </c>
-      <c r="S175" s="22" t="n">
-        <v>-2345</v>
-      </c>
-      <c r="T175" s="22" t="n">
-        <v>-2558</v>
-      </c>
-      <c r="U175" s="22" t="n">
-        <v>-2525</v>
-      </c>
-      <c r="V175" s="22" t="n">
-        <v>-3393</v>
-      </c>
-      <c r="W175" s="22" t="n">
-        <v>-4218</v>
-      </c>
-      <c r="X175" s="22" t="n">
-        <v>-4425</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C176" s="12" t="n">
-        <v>4927</v>
-      </c>
-      <c r="E176" s="12" t="n">
-        <v>-533</v>
-      </c>
-      <c r="G176" s="12" t="n">
-        <v>-2291</v>
-      </c>
-      <c r="I176" s="12" t="n">
-        <v>-4711</v>
-      </c>
-      <c r="K176" s="12" t="n">
-        <v>-2441</v>
-      </c>
-      <c r="M176" s="12" t="n">
-        <v>-8584</v>
-      </c>
-      <c r="O176" s="12" t="n">
-        <v>-1598</v>
-      </c>
-      <c r="P176" s="12" t="n">
-        <v>-2772</v>
-      </c>
-      <c r="Q176" s="12" t="n">
-        <v>-796</v>
-      </c>
-      <c r="R176" s="12" t="n">
-        <v>-2433</v>
-      </c>
-      <c r="S176" s="12" t="n">
-        <v>-2648</v>
-      </c>
-      <c r="T176" s="12" t="n">
-        <v>-2899</v>
-      </c>
-      <c r="U176" s="12" t="n">
-        <v>-6351</v>
-      </c>
-      <c r="V176" s="12" t="n">
-        <v>-533</v>
-      </c>
-      <c r="W176" s="12" t="n">
-        <v>-4711</v>
-      </c>
-      <c r="X176" s="12" t="n">
-        <v>-8584</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="20" t="inlineStr">
         <is>
-          <t>현금성자산 환산차이</t>
-        </is>
-      </c>
-      <c r="C177" s="22" t="n">
-        <v>494</v>
+          <t>단기차입금 순증감</t>
+        </is>
       </c>
       <c r="E177" s="22" t="n">
-        <v>537</v>
-      </c>
-      <c r="G177" s="22" t="n">
-        <v>-112</v>
+        <v>3333</v>
       </c>
       <c r="I177" s="22" t="n">
-        <v>-51</v>
-      </c>
-      <c r="K177" s="22" t="n">
-        <v>193</v>
-      </c>
-      <c r="M177" s="22" t="n">
-        <v>624</v>
-      </c>
-      <c r="O177" s="22" t="n">
-        <v>-204</v>
-      </c>
-      <c r="P177" s="22" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q177" s="22" t="n">
-        <v>-133</v>
-      </c>
-      <c r="R177" s="22" t="n">
-        <v>-164</v>
-      </c>
-      <c r="S177" s="22" t="n">
-        <v>322</v>
+        <v>0</v>
       </c>
       <c r="T177" s="22" t="n">
-        <v>368</v>
+        <v>0</v>
       </c>
       <c r="U177" s="22" t="n">
-        <v>259</v>
+        <v>-629</v>
       </c>
       <c r="V177" s="22" t="n">
-        <v>537</v>
+        <v>3333</v>
       </c>
       <c r="W177" s="22" t="n">
-        <v>-51</v>
-      </c>
-      <c r="X177" s="22" t="n">
-        <v>624</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="20" t="inlineStr">
         <is>
+          <t>장기차입금 상환</t>
+        </is>
+      </c>
+      <c r="C178" s="22" t="n">
+        <v>-76</v>
+      </c>
+      <c r="E178" s="22" t="n">
+        <v>-156</v>
+      </c>
+      <c r="G178" s="22" t="n">
+        <v>-83</v>
+      </c>
+      <c r="I178" s="22" t="n">
+        <v>-163</v>
+      </c>
+      <c r="K178" s="22" t="n">
+        <v>-84</v>
+      </c>
+      <c r="M178" s="22" t="n">
+        <v>-174</v>
+      </c>
+      <c r="O178" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P178" s="22" t="n">
+        <v>-959</v>
+      </c>
+      <c r="Q178" s="22" t="n">
+        <v>-55</v>
+      </c>
+      <c r="R178" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S178" s="22" t="n">
+        <v>-61</v>
+      </c>
+      <c r="T178" s="22" t="n">
+        <v>-130</v>
+      </c>
+      <c r="U178" s="22" t="n">
+        <v>-140</v>
+      </c>
+      <c r="V178" s="22" t="n">
+        <v>-156</v>
+      </c>
+      <c r="W178" s="22" t="n">
+        <v>-163</v>
+      </c>
+      <c r="X178" s="22" t="n">
+        <v>-174</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="20" t="inlineStr">
+        <is>
+          <t>장기차입</t>
+        </is>
+      </c>
+      <c r="P179" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q179" s="22" t="n">
+        <v>1284</v>
+      </c>
+      <c r="R179" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="20" t="inlineStr">
+        <is>
+          <t>리스부채 상환</t>
+        </is>
+      </c>
+      <c r="C180" s="22" t="n">
+        <v>-158</v>
+      </c>
+      <c r="E180" s="22" t="n">
+        <v>-315</v>
+      </c>
+      <c r="G180" s="22" t="n">
+        <v>-151</v>
+      </c>
+      <c r="I180" s="22" t="n">
+        <v>-329</v>
+      </c>
+      <c r="K180" s="22" t="n">
+        <v>-197</v>
+      </c>
+      <c r="M180" s="22" t="n">
+        <v>-402</v>
+      </c>
+      <c r="Q180" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R180" s="22" t="n">
+        <v>-194</v>
+      </c>
+      <c r="S180" s="22" t="n">
+        <v>-240</v>
+      </c>
+      <c r="T180" s="22" t="n">
+        <v>-209</v>
+      </c>
+      <c r="U180" s="22" t="n">
+        <v>-234</v>
+      </c>
+      <c r="V180" s="22" t="n">
+        <v>-315</v>
+      </c>
+      <c r="W180" s="22" t="n">
+        <v>-329</v>
+      </c>
+      <c r="X180" s="22" t="n">
+        <v>-402</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="20" t="inlineStr">
+        <is>
+          <t>자기주식 취득</t>
+        </is>
+      </c>
+      <c r="C181" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I181" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" s="22" t="n">
+        <v>-3582</v>
+      </c>
+      <c r="O181" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P181" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q181" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R181" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S181" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T181" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U181" s="22" t="n">
+        <v>-2821</v>
+      </c>
+      <c r="V181" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W181" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X181" s="22" t="n">
+        <v>-3582</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="20" t="inlineStr">
+        <is>
+          <t>배당금 지급</t>
+        </is>
+      </c>
+      <c r="C182" s="22" t="n">
+        <v>-1337</v>
+      </c>
+      <c r="E182" s="22" t="n">
+        <v>-3393</v>
+      </c>
+      <c r="G182" s="22" t="n">
+        <v>-2056</v>
+      </c>
+      <c r="I182" s="22" t="n">
+        <v>-4218</v>
+      </c>
+      <c r="K182" s="22" t="n">
+        <v>-2160</v>
+      </c>
+      <c r="M182" s="22" t="n">
+        <v>-4425</v>
+      </c>
+      <c r="O182" s="22" t="n">
+        <v>-1598</v>
+      </c>
+      <c r="P182" s="22" t="n">
+        <v>-1812</v>
+      </c>
+      <c r="Q182" s="22" t="n">
+        <v>-2025</v>
+      </c>
+      <c r="R182" s="22" t="n">
+        <v>-2238</v>
+      </c>
+      <c r="S182" s="22" t="n">
+        <v>-2345</v>
+      </c>
+      <c r="T182" s="22" t="n">
+        <v>-2558</v>
+      </c>
+      <c r="U182" s="22" t="n">
+        <v>-2525</v>
+      </c>
+      <c r="V182" s="22" t="n">
+        <v>-3393</v>
+      </c>
+      <c r="W182" s="22" t="n">
+        <v>-4218</v>
+      </c>
+      <c r="X182" s="22" t="n">
+        <v>-4425</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C183" s="12" t="n">
+        <v>4927</v>
+      </c>
+      <c r="E183" s="12" t="n">
+        <v>-533</v>
+      </c>
+      <c r="G183" s="12" t="n">
+        <v>-2291</v>
+      </c>
+      <c r="I183" s="12" t="n">
+        <v>-4711</v>
+      </c>
+      <c r="K183" s="12" t="n">
+        <v>-2441</v>
+      </c>
+      <c r="M183" s="12" t="n">
+        <v>-8584</v>
+      </c>
+      <c r="O183" s="12" t="n">
+        <v>-1598</v>
+      </c>
+      <c r="P183" s="12" t="n">
+        <v>-2772</v>
+      </c>
+      <c r="Q183" s="12" t="n">
+        <v>-796</v>
+      </c>
+      <c r="R183" s="12" t="n">
+        <v>-2433</v>
+      </c>
+      <c r="S183" s="12" t="n">
+        <v>-2648</v>
+      </c>
+      <c r="T183" s="12" t="n">
+        <v>-2899</v>
+      </c>
+      <c r="U183" s="12" t="n">
+        <v>-6351</v>
+      </c>
+      <c r="V183" s="12" t="n">
+        <v>-533</v>
+      </c>
+      <c r="W183" s="12" t="n">
+        <v>-4711</v>
+      </c>
+      <c r="X183" s="12" t="n">
+        <v>-8584</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="20" t="inlineStr">
+        <is>
+          <t>현금성자산 환산차이</t>
+        </is>
+      </c>
+      <c r="C184" s="22" t="n">
+        <v>494</v>
+      </c>
+      <c r="E184" s="22" t="n">
+        <v>537</v>
+      </c>
+      <c r="G184" s="22" t="n">
+        <v>-112</v>
+      </c>
+      <c r="I184" s="22" t="n">
+        <v>-51</v>
+      </c>
+      <c r="K184" s="22" t="n">
+        <v>193</v>
+      </c>
+      <c r="M184" s="22" t="n">
+        <v>624</v>
+      </c>
+      <c r="O184" s="22" t="n">
+        <v>-204</v>
+      </c>
+      <c r="P184" s="22" t="n">
+        <v>110</v>
+      </c>
+      <c r="Q184" s="22" t="n">
+        <v>-133</v>
+      </c>
+      <c r="R184" s="22" t="n">
+        <v>-164</v>
+      </c>
+      <c r="S184" s="22" t="n">
+        <v>322</v>
+      </c>
+      <c r="T184" s="22" t="n">
+        <v>368</v>
+      </c>
+      <c r="U184" s="22" t="n">
+        <v>259</v>
+      </c>
+      <c r="V184" s="22" t="n">
+        <v>537</v>
+      </c>
+      <c r="W184" s="22" t="n">
+        <v>-51</v>
+      </c>
+      <c r="X184" s="22" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="20" t="inlineStr">
+        <is>
           <t>현금성자산 증감</t>
         </is>
       </c>
-      <c r="C178" s="22" t="n">
+      <c r="C185" s="22" t="n">
         <v>4488</v>
       </c>
-      <c r="E178" s="22" t="n">
+      <c r="E185" s="22" t="n">
         <v>6861</v>
       </c>
-      <c r="G178" s="22" t="n">
+      <c r="G185" s="22" t="n">
         <v>2382</v>
       </c>
-      <c r="I178" s="22" t="n">
+      <c r="I185" s="22" t="n">
         <v>4640</v>
       </c>
-      <c r="K178" s="22" t="n">
+      <c r="K185" s="22" t="n">
         <v>-5170</v>
       </c>
-      <c r="M178" s="22" t="n">
+      <c r="M185" s="22" t="n">
         <v>-705</v>
       </c>
-      <c r="O178" s="22" t="n">
+      <c r="O185" s="22" t="n">
         <v>4573</v>
       </c>
-      <c r="P178" s="22" t="n">
+      <c r="P185" s="22" t="n">
         <v>-4399</v>
       </c>
-      <c r="Q178" s="22" t="n">
+      <c r="Q185" s="22" t="n">
         <v>-4295</v>
       </c>
-      <c r="R178" s="22" t="n">
+      <c r="R185" s="22" t="n">
         <v>1842</v>
       </c>
-      <c r="S178" s="22" t="n">
+      <c r="S185" s="22" t="n">
         <v>940</v>
       </c>
-      <c r="T178" s="22" t="n">
+      <c r="T185" s="22" t="n">
         <v>3505</v>
       </c>
-      <c r="U178" s="22" t="n">
+      <c r="U185" s="22" t="n">
         <v>-12830</v>
       </c>
-      <c r="V178" s="22" t="n">
+      <c r="V185" s="22" t="n">
         <v>6861</v>
       </c>
-      <c r="W178" s="22" t="n">
+      <c r="W185" s="22" t="n">
         <v>4640</v>
       </c>
-      <c r="X178" s="22" t="n">
+      <c r="X185" s="22" t="n">
         <v>-705</v>
       </c>
     </row>
@@ -10280,7 +10751,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -11710,7 +12181,7 @@
       <c r="L42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -11762,7 +12233,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="46" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -11814,7 +12285,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -11866,7 +12337,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="46" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -11918,7 +12389,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="46" t="inlineStr">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -11970,7 +12441,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -12022,7 +12493,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="46" t="inlineStr">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -12032,43 +12503,43 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="48">
         <f>IFERROR(IF((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="48">
+      <c r="D49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="48">
+      <c r="F49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="48">
+      <c r="G49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="47">
+      <c r="H49" s="48">
         <f>IFERROR(IF(('연간'!T44)&lt;=0,"적자",H28/('연간'!T44)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="48">
+      <c r="I49" s="49">
         <f>IFERROR(IF(('연간'!U44)&lt;=0,"적자",I28/('연간'!U44)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="48">
+      <c r="J49" s="49">
         <f>IFERROR(IF(('연간'!V44)&lt;=0,"적자",J28/('연간'!V44)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="48">
+      <c r="K49" s="49">
         <f>IFERROR(IF(('연간'!W44)&lt;=0,"적자",K28/('연간'!W44)),"")</f>
         <v/>
       </c>
-      <c r="L49" s="48">
+      <c r="L49" s="49">
         <f>IFERROR(IF(('연간'!X44)&lt;=0,"적자",L28/('연간'!X44)),"")</f>
         <v/>
       </c>
@@ -12092,7 +12563,7 @@
       <c r="L50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -12144,7 +12615,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="46" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -12196,7 +12667,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="46" t="inlineStr">
+      <c r="A53" s="47" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -12248,7 +12719,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="46" t="inlineStr">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -12300,7 +12771,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -12352,7 +12823,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -12422,7 +12893,7 @@
       <c r="L57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="46" t="inlineStr">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -12474,7 +12945,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -12484,49 +12955,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="50">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="50">
+      <c r="D59" s="51">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="50">
+      <c r="E59" s="51">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="51">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="50">
+      <c r="G59" s="51">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="49">
+      <c r="H59" s="50">
         <f>IFERROR(H8/('연간'!T4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="51">
         <f>IFERROR(I8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="50">
+      <c r="J59" s="51">
         <f>IFERROR(J8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="50">
+      <c r="K59" s="51">
         <f>IFERROR(K8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="L59" s="50">
+      <c r="L59" s="51">
         <f>IFERROR(L8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="46" t="inlineStr">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -12536,49 +13007,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>IFERROR(C9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="50">
+      <c r="D60" s="51">
         <f>IFERROR(D9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="50">
+      <c r="E60" s="51">
         <f>IFERROR(E9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="50">
+      <c r="F60" s="51">
         <f>IFERROR(F9/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="50">
+      <c r="G60" s="51">
         <f>IFERROR(G9/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="49">
+      <c r="H60" s="50">
         <f>IFERROR(H9/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="50">
+      <c r="I60" s="51">
         <f>IFERROR(I9/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="50">
+      <c r="J60" s="51">
         <f>IFERROR(J9/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="50">
+      <c r="K60" s="51">
         <f>IFERROR(K9/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L60" s="50">
+      <c r="L60" s="51">
         <f>IFERROR(L9/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="46" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -12588,49 +13059,49 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="50">
         <f>IFERROR(C19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="50">
+      <c r="D61" s="51">
         <f>IFERROR(D19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="51">
         <f>IFERROR(E19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="50">
+      <c r="F61" s="51">
         <f>IFERROR(F19/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="50">
+      <c r="G61" s="51">
         <f>IFERROR(G19/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="49">
+      <c r="H61" s="50">
         <f>IFERROR(H19/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="50">
+      <c r="I61" s="51">
         <f>IFERROR(I19/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="50">
+      <c r="J61" s="51">
         <f>IFERROR(J19/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="50">
+      <c r="K61" s="51">
         <f>IFERROR(K19/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L61" s="50">
+      <c r="L61" s="51">
         <f>IFERROR(L19/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="46" t="inlineStr">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -12640,43 +13111,43 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="50">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="50">
+      <c r="D62" s="51">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="50">
+      <c r="E62" s="51">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="51">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="50">
+      <c r="G62" s="51">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="49">
+      <c r="H62" s="50">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="50">
+      <c r="I62" s="51">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="50">
+      <c r="J62" s="51">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="50">
+      <c r="K62" s="51">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
-      <c r="L62" s="50">
+      <c r="L62" s="51">
         <f>IF(OR(L59="",L60="",L61=""),"",IFERROR(L59+L60-L61,""))</f>
         <v/>
       </c>
@@ -12700,7 +13171,7 @@
       <c r="L63" s="25" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="46" t="inlineStr">
+      <c r="A64" s="47" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -12752,7 +13223,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="46" t="inlineStr">
+      <c r="A65" s="47" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -12804,7 +13275,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="46" t="inlineStr">
+      <c r="A66" s="47" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -12856,7 +13327,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="46" t="inlineStr">
+      <c r="A67" s="47" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -15050,24 +15521,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="52" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="52" t="inlineStr">
+      <c r="B3" s="53" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="52" t="inlineStr">
+      <c r="C3" s="53" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
